--- a/formulario_escuela_nueva.xlsx
+++ b/formulario_escuela_nueva.xlsx
@@ -1,24 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B91087B-07C0-4C80-8A93-CF686C3A382A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Respuestas" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Respuestas" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Respuestas!$A$1:$U$3</definedName>
-  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="632">
   <si>
     <t>Municipio</t>
   </si>
@@ -83,15 +76,389 @@
     <t>Observación 9</t>
   </si>
   <si>
+    <t>Aguadas</t>
+  </si>
+  <si>
+    <t>El Edén</t>
+  </si>
+  <si>
     <t>Verde</t>
   </si>
   <si>
     <t>Aplica</t>
   </si>
   <si>
+    <t xml:space="preserve">Ya existe, para, la vigencia responsable de los Microcentros y apropiación de materiales para ambientar. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya existe asignación por Resolución. </t>
+  </si>
+  <si>
+    <t>No aplica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En el plan de estudios no se evidencia este campo de saber. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">De prácticas a procesos y de manera cotidiana en la mayoría de las sedes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gobierno Escolar conforme al decreto a la Ley 115 de 1994.y gobiernos de aula en las sedes Uni docente. </t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t xml:space="preserve">Hay metodologías y responsabkes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las instancias de Gobierno Escolar b trabajando mediante bla teoría de equipos. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se utiliza el material impreso por la Alianza. </t>
+  </si>
+  <si>
+    <t>Encimadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se tiene en cuenta que en las aulas se debe responder al modelo con la decoración adecuada. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se encuentra organizada la junta de Microcentro y cada uno de los comités. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde el grado cuarto a noveno se maneja la hora de emprendimiento y en 10 y 11 trabajamos gestión de negocios. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los docentes en el trabajo diario implementan buzones de compromisos y sugerencias, correos de aula, decálogos de aula. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">El gobierno estudiantil se tiene estructurado en la IE Encimadas, sin embargo, para su inicio presenta dificultades para su fundamentación. La IE Encimadas lo tiene adecuado general con un presidente de cada una de las sedes elegido en actividades democráticas. Hay encuentros periódicos que arrojan necesidades y actividades para trabajar en cada una de las sedes y que además fortalezcan el liderazgo y la participación de cada una de los estudiantes en sus sedes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En la IE Encimadas se trabajan las actividades de conjunto dos veces por semana. </t>
+  </si>
+  <si>
+    <t>La comunidad educativa es consciente de la necesidad de los equipos de trabajo, áreas de gestión, consejo de padres, consejo de estudiantes…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los docentes articulan el trabajo en las aulas multigrado, con el trabajo de las guías de auto aprendizaje, los docentes utilizan las guías que existen y además, generan acciones de adaptación. </t>
+  </si>
+  <si>
+    <t>La Mermita</t>
+  </si>
+  <si>
+    <t>Se decoran y ambientan con materiales intencionados buscando apoyos en DUA y fortalecimiento del modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se desarrollan en las sedes con la participación de la comunidad educativa </t>
+  </si>
+  <si>
+    <t>Se maneja desde la cultura del emprendimiento y como área optativa para fortalecer ideas de negocios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se utilizan como estrategia de apoyo al gobierno estudiantil y buscan fortalecer competencias </t>
+  </si>
+  <si>
+    <t>Se elige democráticamente y funciona para fortalecer la administración escolar</t>
+  </si>
+  <si>
+    <t>Se desarrollan por parte de los estudiantes al inicio de las jornadas escolares con planeaciones anticipadas</t>
+  </si>
+  <si>
+    <t>Se maneja constantemente de acuerdo al modelo escuela nueva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se usan en buen porcentaje, con adaptaciones por parte de los docentes </t>
+  </si>
+  <si>
+    <t>Rioarriba</t>
+  </si>
+  <si>
+    <t>Decoración y renovación de acuerdo al model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se desarrolla con ls componentes y Comités en las sedes seleccionadas y preparadas para el evento </t>
+  </si>
+  <si>
+    <t>Se trebajan dos horas semanales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los instrumentos son revisados y verificada su funcionamiento intensionando las competencias  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Funcionamiento con gran compromiso </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las realizan  el gobierno estuantil con la asesoría de los docentes </t>
+  </si>
+  <si>
+    <t>Trabajo permanente entregando y mostrando resultados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si se estan trabajando </t>
+  </si>
+  <si>
+    <t>San Antonio de Arma</t>
+  </si>
+  <si>
+    <t>En las escuelas multigrado.  En la ie se maneja un modelo pedagógico crítico, constructivista donde la secundaria trabaja por aulas especializadas.</t>
+  </si>
+  <si>
+    <t>Ya están con los roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se maneja en la asignación académica </t>
+  </si>
+  <si>
+    <t xml:space="preserve">De acuerdo con lo reglamentario de ley, cada aprobación de modificación a documentos como siete y pei se hace con estamentos del gobierno escolar, y en toma de decisiones con representatividades en el comité de convivencia, consejos. </t>
+  </si>
+  <si>
+    <t>Se hace cronograma a comienzo de año y se cumple las funciones y respeto a la 1620.</t>
+  </si>
+  <si>
+    <t>Es para ambientar todos los procesos de la escuela al iniciar las actividades que se programa en cada sesión .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trabajo en cooperación se realiza en la escuela </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En las sedes multigrado </t>
+  </si>
+  <si>
+    <t>Viboral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funcionan bien en las primarias </t>
+  </si>
+  <si>
+    <t>Todos</t>
+  </si>
+  <si>
+    <t>En horario institucional</t>
+  </si>
+  <si>
+    <t>Funciona bien en las primarias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se elige en el salón de clase </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al inicio de clase por lo general </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generalmente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se adecuan según la necesidad </t>
+  </si>
+  <si>
+    <t>Anserma</t>
+  </si>
+  <si>
+    <t>Gómez Fernandez</t>
+  </si>
+  <si>
+    <t>Se aplican algunas decoraciones con los instrumentos de escuela nueva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se desarrollan en el año los propuestos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se trabaja como emprendimiento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se cuenta mínimo con 3 instrumentos por aula </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se desarrollan el trabajo en los grupos y se dinamizan actividades como las actividades de conjunto </t>
+  </si>
+  <si>
+    <t>Se direccionan con el director de grupo</t>
+  </si>
+  <si>
+    <t>Se realizan las mesas de trabajo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizan los ajustes y se crean guías nuevas según las necesidades </t>
+  </si>
+  <si>
+    <t>Jerónimo de Tejelo</t>
+  </si>
+  <si>
+    <t>La mayoría lo aplican pero existe un 30% Aprox que no lo hacen</t>
+  </si>
+  <si>
+    <t>Se realizan al menosv3 en el año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En la Asigns8de Emprendimiento y Agropecuaria </t>
+  </si>
+  <si>
+    <t>Muchos docentes no lo aplican en la IE</t>
+  </si>
+  <si>
+    <t>Se realiza en la mayoría de los grados y grupos</t>
+  </si>
+  <si>
+    <t>Se trabaja por grupos de gestiónes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De usan en la mayoría de los grados y grupos </t>
+  </si>
+  <si>
+    <t>Juan XXIII</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>4 por año</t>
+  </si>
+  <si>
+    <t>Si, en cada aula</t>
+  </si>
+  <si>
+    <t>Si, a la primera hora</t>
+  </si>
+  <si>
+    <t>Ocuzca</t>
+  </si>
+  <si>
+    <t>Se aprecian daños en las aulas.</t>
+  </si>
+  <si>
+    <t>Se desarrollan, pero hay limitaciones por parte de la secretaría.</t>
+  </si>
+  <si>
+    <t>Se cumple.</t>
+  </si>
+  <si>
+    <t>Se usan en las actividades de conjunto.</t>
+  </si>
+  <si>
+    <t>Se desarrollan las todas las fases y se promueve su integración en todas las actividades institucionales.</t>
+  </si>
+  <si>
+    <t>Se desarrollan las generales y de Aula.</t>
+  </si>
+  <si>
+    <t>Es el pilar fundamental.</t>
+  </si>
+  <si>
+    <t>El maestro las evalúa e integra en su trabajo.</t>
+  </si>
+  <si>
+    <t>San Pedro</t>
+  </si>
+  <si>
+    <t>Son pertinentes y ajustados a la necesidad del contexto y a la capacidad que se requiere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con base al cronograma y orientaciones de la red de maestros
+</t>
+  </si>
+  <si>
+    <t>Articulada con la profundización en emprendimiento y turismo con la que curnta el EE</t>
+  </si>
+  <si>
+    <t>Cada uno de sus elementos constitutivos se refuerza en las sedes unitarias y en la sede central opera bajo la brújula del Proyecto Pedagógico Transversal de Democracia</t>
+  </si>
+  <si>
+    <t>Se cuenta con un plan de acción con su respectivo cronograma de actividades, los docentes líderes del proceso y acompañamiento en la ejecución y evaluación del impacto</t>
+  </si>
+  <si>
+    <t>La realización de las actividades de conjunto se ha venido desarrollando como una puesta en común que está direccionada a partir de un cronograma y que se ejecuta semanalmente</t>
+  </si>
+  <si>
+    <t>Se fomenta como politica institucional</t>
+  </si>
+  <si>
+    <t>En función de la actualización del componente curricular en concordancia con los lineamientos curriculares y referentes de calidad emitidos por el MEN, los docentes se han dado a la tarea de construir sus propias guías de interaprendizaje apuntando a las necesidades del contexto y los requerimientos para abordar pruebas externas</t>
+  </si>
+  <si>
+    <t>Aranzazu</t>
+  </si>
+  <si>
+    <t>Alegrías</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si son ambientadas de acuerdo al modelo </t>
+  </si>
+  <si>
+    <t>Opera pero el módulo no se trabaja en su totalidad sin embargo se tiene proyectos productivos como evidencia del modulo</t>
+  </si>
+  <si>
+    <t>Si se definen algunos al inicio del año y son operativos durante el año</t>
+  </si>
+  <si>
+    <t>Si es operativo  hay gobierno de aula y gobierno general</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Junta directiva opera adecuadamente planea los microcentros y los docentes tiene muy buena disponibilidad </t>
+  </si>
+  <si>
+    <t>Se planean y ejecutan adecuadamente tres veces por semana</t>
+  </si>
+  <si>
+    <t>Excelente el trabajo en equipo de todos los docentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En algunas áreas ya que otras son muy obsoletas, sin embargo la metodología  es aplicada  con las guías que los docentes elaboran </t>
+  </si>
+  <si>
+    <t>Juan Crisóstomo Osorio</t>
+  </si>
+  <si>
+    <t>Las aulas en cada una de las 11 Sedes Educativas se ambientan con material didáctico y pedagógico de Escuela Nueva.</t>
+  </si>
+  <si>
+    <t>Los docentes participan en los microcentros sin embargo es una oportunidad de Mejoramiento en la Institución Educativa.</t>
+  </si>
+  <si>
+    <t>Se desarrolla en el área de emprendimiento.</t>
+  </si>
+  <si>
+    <t>Se aplican y utilizan instrumentos de Aula en cada una de las Sedes Educativas.</t>
+  </si>
+  <si>
+    <t>Opera actualmente con normalidad en cada grado, elegido y organizado por los directores de grupo.</t>
+  </si>
+  <si>
+    <t>Se organizan y aplican a diario o mínimo semanalmente en cada una de las Sedes Educativas.</t>
+  </si>
+  <si>
+    <t>Excelente Equipo de Trabajo en Equipo y Clima Insritucional.</t>
+  </si>
+  <si>
+    <t>Teniendo en cuenta el modelo se implementan en cada una de las Áreas.</t>
+  </si>
+  <si>
+    <t>Pío XI</t>
+  </si>
+  <si>
+    <t>Muy bien</t>
+  </si>
+  <si>
+    <t>No tengo conocimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumplen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funciona bien, apoyo a los docentes
+</t>
+  </si>
+  <si>
+    <t>Todos al inicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docente rurales organizados </t>
+  </si>
+  <si>
+    <t>No todos tienen las guías en la última asesoría quedamos de descargarlas y enviarselas</t>
+  </si>
+  <si>
     <t>Belalcázar</t>
   </si>
   <si>
@@ -141,19 +508,1427 @@
   </si>
   <si>
     <t>Es funcional</t>
+  </si>
+  <si>
+    <t>Chinchiná</t>
+  </si>
+  <si>
+    <t>Eduardo Gómez Arrubla</t>
+  </si>
+  <si>
+    <t>Las aulas se cuentan ambientadas con relación a los instrumentos de gobierno estudiantil.</t>
+  </si>
+  <si>
+    <t>Se cuenta con la hora de Gestión de Negocios de manera adecuada a partir de grado cuarto hasta once.</t>
+  </si>
+  <si>
+    <t>Se cuenta en las aulas con los instrumentos de gobierno estudiantil para su dinamización.</t>
+  </si>
+  <si>
+    <t>Se aplica de manera adecuada en las primarias. Se necesita fortalecer en posprimaria y media en cuanto a su operatividad.</t>
+  </si>
+  <si>
+    <t>Los docentes se encuentran organizados por junta directiva y cada uno de sus componentes para la dinamización de los microcentros.</t>
+  </si>
+  <si>
+    <t>Se realizan las actividades de conjunto de la siguiente manera: una de manera general cada 15 días y luego se hacen 2 en cada grado a la semana.</t>
+  </si>
+  <si>
+    <t>Se realiza de manera adecuada en la institución educativa y sus sedes.</t>
+  </si>
+  <si>
+    <t>Se aplica pero es necesario actualizar el material en primaria, posprimaria y media para una mejor dinamización.</t>
+  </si>
+  <si>
+    <t>El Trébol</t>
+  </si>
+  <si>
+    <t>Rojo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algunas sedes han ambientado el aula. Sin embargo, requiere de fortalecimiento para que se aplique al 100% en los grados y sedes </t>
+  </si>
+  <si>
+    <t>Se requiere hacer las adecuaciones pedagógicas y logísticas para su  adopción institucional.</t>
+  </si>
+  <si>
+    <t>Se requiere fortalecer el proceso pues se hace aplicación en algunas sedes y grados.</t>
+  </si>
+  <si>
+    <t>Se requiere fortalecer el componente en Básica Primaria, Secundaria y Media, pues su aplicación se realiza en algunas sedes y grados.</t>
+  </si>
+  <si>
+    <t>Los docentes y directivos docentes han realizado el proceso organizativo y logístico de la mejor manera, llevando a cabo la agenda planteada para casa encuentro.</t>
+  </si>
+  <si>
+    <t>En la mayoría de las sedes se aplica. Sin embargo, se requiere fortalecer el componente a nivel general a través de capacitaciones y actualizaciones para los docentes.</t>
+  </si>
+  <si>
+    <t>Se requiere fortalecer el proceso para generar impactos reales y significativos a nivel institucional.</t>
+  </si>
+  <si>
+    <t>Se requiere mayor dotación para trabajar al 100% con cada grado y sede.</t>
+  </si>
+  <si>
+    <t>Filadelfia</t>
+  </si>
+  <si>
+    <t>Antonio Nariño</t>
+  </si>
+  <si>
+    <t>Las aulas están decoradas con los instrumentos de escuela nueva</t>
+  </si>
+  <si>
+    <t>Se trabajo en decimo y once</t>
+  </si>
+  <si>
+    <t>Existe el gobierno estudiantil en cada una de la sedes</t>
+  </si>
+  <si>
+    <t>Todas las sedes cumplen muy bien con este mecanismo.</t>
+  </si>
+  <si>
+    <t>Los docentes particpan activamente de los micorocentrso</t>
+  </si>
+  <si>
+    <t>En todas alas sedes la a actividades de conjunto se realizan</t>
+  </si>
+  <si>
+    <t>Algunas sedes tienen problamas para que los estudiantes para trabjar en mesas exagonales</t>
+  </si>
+  <si>
+    <t>Además de usar las guías, los docentes hacen adaptaciones</t>
+  </si>
+  <si>
+    <t>Crisanto Luque</t>
+  </si>
+  <si>
+    <t>en general bien</t>
+  </si>
+  <si>
+    <t>aplica en todas las sedes posprimarias</t>
+  </si>
+  <si>
+    <t>cada sede maneja los que considere</t>
+  </si>
+  <si>
+    <t>bien en general</t>
+  </si>
+  <si>
+    <t>funciona bien</t>
+  </si>
+  <si>
+    <t>bien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">el trabajo por mesa es poco </t>
+  </si>
+  <si>
+    <t xml:space="preserve">se han realizado adaptaciones propias </t>
+  </si>
+  <si>
+    <t>La Dorada</t>
+  </si>
+  <si>
+    <t>Buenavista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No hace falta mejorar la ambientación por priorización de recursos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo tenemos como área incluye las asignaturas turismo por nuestro horizonte institucional y emprendimiento e innovación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se observa medianamente por recursos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nos hace falta inversión en dotación en los ambientes desde mobiliario hasta los rincones de los espacios del gobierno por grado la institución práctica ambientes especializados </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizan conforme a la propuesta salvo disposiciones de la secretaría departamental </t>
+  </si>
+  <si>
+    <t>Hace falta más seguimiento en los momentos de clase debido a nuestro contexto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Política institucional </t>
+  </si>
+  <si>
+    <t>Se requiere articular con otras estrategias asociadas colegios amigos del turismo y sena</t>
+  </si>
+  <si>
+    <t>El Japón</t>
+  </si>
+  <si>
+    <t>Idem.</t>
+  </si>
+  <si>
+    <t>Se tiene un docente encargado de dictar la asignatura de Gestión de Negocios en la media.</t>
+  </si>
+  <si>
+    <t>En los microcentros se ha tocado el tema de los instrumentos de gobierno y ya los docentes se pusieron a la tarea de tener los instrumentos en cada aula.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La docente de Ciencias Sociales ha sido muy juiciosa con el tema del Gobierno Estudiantil y está operando con normalidad en la Institución. </t>
+  </si>
+  <si>
+    <t>Los docentes que conforman el Comité de Escuela Nueva han sido muy juiciosos y organizados con la planeación cada año de los microcentros cumpliendo con las expectativas.</t>
+  </si>
+  <si>
+    <t>En los microcentros se ha hecho mucho énfasis en que los docentes las realicen como inicio de las actividades.</t>
+  </si>
+  <si>
+    <t>Excelente grupo humano.</t>
+  </si>
+  <si>
+    <t>Desafortunadamente, la plataforma de Escuela Virtual se encuentra inhabilitada ya hace un tiempo, por lo que les ha quedado complicado a los docentes descargar las guías de aprendizaje.</t>
+  </si>
+  <si>
+    <t>La Merced</t>
+  </si>
+  <si>
+    <t>La Felisa</t>
+  </si>
+  <si>
+    <t>Se debe fortalecer desde el modelo</t>
+  </si>
+  <si>
+    <t>Se orienta de 6 a 9. Se requieren guías de educación básica.</t>
+  </si>
+  <si>
+    <t>Es importante generalizarlo, adaptarlo al modelo y edades.</t>
+  </si>
+  <si>
+    <t>Se cuenta con dos docentes que lideran. Se tienen gobiernos de aula.</t>
+  </si>
+  <si>
+    <t>Están organizados en microcentros. Se requiere proceso organizativo</t>
+  </si>
+  <si>
+    <t>Se requiere fortalecer, fundamentar dimensionarlas, recrearlas.</t>
+  </si>
+  <si>
+    <t>Política institucional el modelo</t>
+  </si>
+  <si>
+    <t>Falta emprendimiento 6 a 9, carencia de guías de primaria.</t>
+  </si>
+  <si>
+    <t>Parcialmente en algunos grados.</t>
+  </si>
+  <si>
+    <t>Cátedra de emnprendimiento, se trabaja en todos los niveles y grados. Se transversaliza en gestión de negocios.</t>
+  </si>
+  <si>
+    <t>Se maneja parcialmente.</t>
+  </si>
+  <si>
+    <t>Sería importante abordar fundamentación y acompañamiento a la estrategia y la manera cómo ase articula al gobierno escolar. Este ejercicio debería hacerse con los docentes.</t>
+  </si>
+  <si>
+    <t>Los docentes están organizados en microcentros. Los temas de los microcentros se han centrado en el fortalecimiento del modelo. Se debe motivar y acompañar los docentes en planeación y realización.</t>
+  </si>
+  <si>
+    <t>Aplica parcialmente, algunos docentes las planean otros no. Debe fortalecerse su aplicación.</t>
+  </si>
+  <si>
+    <t>Se dinamiza parcialmente, necesidad de mobiliario y guías.</t>
+  </si>
+  <si>
+    <t>Aplica con oportunidades de mejora, bajo el concepto de desactualización. Necesidades secundaria y media de actualización.</t>
+  </si>
+  <si>
+    <t>Manzanares</t>
+  </si>
+  <si>
+    <t>Aguabonita</t>
+  </si>
+  <si>
+    <t>La ambientación se hace cada al comienzo de cada año, en este momento cada directos de grupo esta en ese proceso</t>
+  </si>
+  <si>
+    <t>esta en nuestro currículo como parte importante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">el manejo de los instrumentos de aula se aplican de forma regular </t>
+  </si>
+  <si>
+    <t>El gobierno estudiantil se organiza en todas sus etapas, desde la conformación de los integrantes, la operatividad  en las aulas y el colegio como tal.</t>
+  </si>
+  <si>
+    <t>los docentes de la institución se han apropiado de este mecanismo de integración, capacitación</t>
+  </si>
+  <si>
+    <t>Este año las actividades de conjunto se esta  desarrollando en los primeros 15 minutos de clase con su respectivo director de grupo ,en nuestro análisis queremos que sean mas dinámicas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuestra institución es consciente de la importancia de tener un grupo articulado y unido con el propósito de mejorar cada dia </t>
+  </si>
+  <si>
+    <t>Los docentes utilizan las guías de forma regular aunque veo con preocupación que en algunos temas y contenidos estan un poco desactualizadas</t>
+  </si>
+  <si>
+    <t>Gregorio Gutiérrez González</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debemos fortalecer los CRA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existe junta directiva y se gestiona los 4 microcentro Institucionales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza </t>
+  </si>
+  <si>
+    <t>Se priorizan según las necesidades y los aliados estratégicos vinculados</t>
+  </si>
+  <si>
+    <t>Se cumple con la normativa en tiempos estretegicas y empoderamientos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizan semanalmente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debemos fortalecer el manejo de roles y la distribución espacial </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debemos actualizar los módulos , se.untwncionan y adaptan según las necesidades contextuales </t>
+  </si>
+  <si>
+    <t>José Antonio Galán</t>
+  </si>
+  <si>
+    <t>Falta ambientar con elementos propios del modelo.</t>
+  </si>
+  <si>
+    <t>Todos participan y es muy funcional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se trabaja adecuadamente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No se han definido unos institucionales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se desarrolla en toda la institución y es muy operativo. </t>
+  </si>
+  <si>
+    <t>Se realizan una vez por semana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El trabajo en equipo es evidenciado desde todas las prácticas de la institución. </t>
+  </si>
+  <si>
+    <t>Se alternan con otros módulos de inter aprendizaje. Pero se conserva la estructura propuesta por el modelo.</t>
+  </si>
+  <si>
+    <t>Romeral</t>
+  </si>
+  <si>
+    <t>En secundaria es minima</t>
+  </si>
+  <si>
+    <t>En Media</t>
+  </si>
+  <si>
+    <t>Se aplica en primaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se hace la elección pero no es operativo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principalmente los docentes de primaria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se aplica en primaria </t>
+  </si>
+  <si>
+    <t>No se percibe que los estudiantes trabajen en equipo a pesar que están integrados</t>
+  </si>
+  <si>
+    <t>Algunas guías están obsoletas</t>
+  </si>
+  <si>
+    <t>Marmato</t>
+  </si>
+  <si>
+    <t>Cabras</t>
+  </si>
+  <si>
+    <t>Se cumple con la exigencia del modelo</t>
+  </si>
+  <si>
+    <t>Esta desde octavo hasta once. Una hora octavo y noveno y 2 en 10 y 11.</t>
+  </si>
+  <si>
+    <t>No todos algunos</t>
+  </si>
+  <si>
+    <t>Se desarrolla proceso con sus etapas pero hay fallas en el cumplimiento de sus funciones</t>
+  </si>
+  <si>
+    <t>Se elige comite y se realizan todos los microcentros.</t>
+  </si>
+  <si>
+    <t>Esta actividad se suspendio ya que no cumplio el objetivo y se convirtio en una perdedera de tiempo.</t>
+  </si>
+  <si>
+    <t>Docentes integrados y se trabaja en los diferentes proyectos</t>
+  </si>
+  <si>
+    <t>Se sigue la estructura del modelo con información actualizada de otos autores. En algunas áreas se utilizan las guiás.</t>
+  </si>
+  <si>
+    <t>El Llano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcialmente </t>
+  </si>
+  <si>
+    <t>Se trabaja en los grados Décimo y undecimo</t>
+  </si>
+  <si>
+    <t>Los instrumentos del gobierno son parcialmente</t>
+  </si>
+  <si>
+    <t>Se aplica parcialmente en los niños de primaria y algunos grupos de secundaria</t>
+  </si>
+  <si>
+    <t>Se realizan los cuatro microcentros en el año</t>
+  </si>
+  <si>
+    <t>Las actividades de conjunto de realizan parcialmente</t>
+  </si>
+  <si>
+    <t>Algunos docentes trabajan en equipo con sus estudiante</t>
+  </si>
+  <si>
+    <t>Las guías deben ser más actualizadas</t>
+  </si>
+  <si>
+    <t>General Ramón Marín</t>
+  </si>
+  <si>
+    <t>Se cuenta con una ambientación adecuada, se hace más evidente en la primaria.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se trabaja en la media como administración </t>
+  </si>
+  <si>
+    <t>Se presentan algunas debilidades en la aplicación.</t>
+  </si>
+  <si>
+    <t>Se aplica en toda la institución.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El año anterior se cumplió con lo programado </t>
+  </si>
+  <si>
+    <t>Se hacen unos días a la semana, no todos los días.</t>
+  </si>
+  <si>
+    <t>En la mayoría de las actividades.</t>
+  </si>
+  <si>
+    <t>Las guías de básica primaria se encuentran desactualizadas.</t>
+  </si>
+  <si>
+    <t>Se realiza con algunos elementos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No se tiene guías actualizadas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se usan algunos instrumentos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si, apoica, aunque todas las sedes no manejan el modelo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si. Se realiza y se planean a partir de lo propuestas de la Red </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizan tratando de ofrecer el espacio de participación, en baja media </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si, se plantea para fortalecer esta competencia </t>
+  </si>
+  <si>
+    <t>No se poseen guías actualizas para todas las áreas. Los docentes hacen ajustes de las guias</t>
+  </si>
+  <si>
+    <t>Rafael Pombo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El aula se organiza de acuerdo a la propuesta del modelo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se trabaja en la media </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se manejan los instrumentos propuestos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se conforma y cumple sus funciones </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizan los microcentros planeados </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizan generales 2 días a la semana y en el aula 3 días. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En los ambientes de aprendizaje se refleja los grupos de trabajo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se cuenta con las guías del modelo y propias del docente </t>
+  </si>
+  <si>
+    <t>Marquetalia</t>
+  </si>
+  <si>
+    <t>Antonio María Hincapié</t>
+  </si>
+  <si>
+    <t>Se efectua en toda la institución.</t>
+  </si>
+  <si>
+    <t>Se articula en la asignación de agropecuarias, áreas optativas.</t>
+  </si>
+  <si>
+    <t>Se aplica en básica primaria.</t>
+  </si>
+  <si>
+    <t>Se implementa con articulación al consejo estudiantil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza en la institución </t>
+  </si>
+  <si>
+    <t>Se aplica en primaria diaria, en secundaria 2veces a la semana.</t>
+  </si>
+  <si>
+    <t>Fundamenta el trabajo escolar en todos los grados.</t>
+  </si>
+  <si>
+    <t>Se realizan adaptaciones cuando se hace necesario.</t>
+  </si>
+  <si>
+    <t>El Placer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se cuenta con instrumentos seleccionados </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se desarrolla teniendo en cuenta programación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se cuenta con registro de actas y plan de trabajo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se cuenta con gobierno conformado en la vigencia anterior 
+Cuenta con plan de trabajo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se cuenta con plan de trabajo y junta </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se cuenta con días asignados para su desarrollo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se desarrolla la estrategia en las aulas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se utilizan en algunos grados o como material de apoyo </t>
+  </si>
+  <si>
+    <t>La Quiebra</t>
+  </si>
+  <si>
+    <t>Se realiza la ambientación en todas la aulas.</t>
+  </si>
+  <si>
+    <t>Se trabaja gestión de negocios.</t>
+  </si>
+  <si>
+    <t>Se realizan en todos los grados, las implementan en mayor algunos docentes.</t>
+  </si>
+  <si>
+    <t>Se trabaja en todos los niveles pero no de forma continua, es intermitente.</t>
+  </si>
+  <si>
+    <t>Se trabajan los microcentros según las orientaciones.</t>
+  </si>
+  <si>
+    <t>Se promueve el trabajo en equipo.</t>
+  </si>
+  <si>
+    <t>Se maneja en todos los niveles.</t>
+  </si>
+  <si>
+    <t>Patio Bonito</t>
+  </si>
+  <si>
+    <t>Se están unificando criterios en la institución para tener mayor uniformidad.</t>
+  </si>
+  <si>
+    <t>La manejamos como emprendimiento.</t>
+  </si>
+  <si>
+    <t>Es necesario más formación para los docentes.</t>
+  </si>
+  <si>
+    <t>Funciona muy bien en las Sedes Primarias, se debe fortalecer en la Postprimaria.</t>
+  </si>
+  <si>
+    <t>El año 2025, se pudo consolidar un buen equipo.</t>
+  </si>
+  <si>
+    <t>Se hacen oportunamente y con la intención establecida por el modelo.</t>
+  </si>
+  <si>
+    <t>Es bueno, pero sería ideal fortalecerlo.</t>
+  </si>
+  <si>
+    <t>Ideal tener más guías impresas.</t>
+  </si>
+  <si>
+    <t>Neira</t>
+  </si>
+  <si>
+    <t>Aguacatal</t>
+  </si>
+  <si>
+    <t>Se debe mejorar la ambientación de las aulas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La junta está constituida </t>
+  </si>
+  <si>
+    <t>No la hay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se manejan algunos de los instrumentos de gobierno estudiantil </t>
+  </si>
+  <si>
+    <t>El gobierno estudiantil se lleva cada año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las actividades de conjunto de realizándose hay muy buena participación de los estudiantes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza varios trabajos en equipo </t>
+  </si>
+  <si>
+    <t>Los docentes tienen encuesta las guías  para sus clases</t>
+  </si>
+  <si>
+    <t>Llanogrande</t>
+  </si>
+  <si>
+    <t>Por la metodología de rotación en aulas por docentes si aplica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flexibilidad institucional y rescatar los microcentros municipales. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se da como emprendimiento. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En básica primaria y secundaria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con énfasis convivencia institucional </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primero la coordinación municipal por parte del Padrino y en la institución coordinación desde los planes de área.  </t>
+  </si>
+  <si>
+    <t>Pío XII</t>
+  </si>
+  <si>
+    <t>Amarillo</t>
+  </si>
+  <si>
+    <t>Falta de compromiso docente sobre todo en bachillerato y media ya que laboran como si fueran catedráticos.</t>
+  </si>
+  <si>
+    <t>Se desarrollaron los microcentros planeados. Falta revivir el microcentro municipal.</t>
+  </si>
+  <si>
+    <t>Se da como hora de emprendimiento.</t>
+  </si>
+  <si>
+    <t>Falta implementar su uso de manera más práctica.</t>
+  </si>
+  <si>
+    <t>Se elige y funciona en todas sus instancias.</t>
+  </si>
+  <si>
+    <t>Se deben fortalecer y que sean realizadas por los mlsmos estudiantes.</t>
+  </si>
+  <si>
+    <t>Falta implementar el modelo escuela nueva de manera práctica ya qud funciona como si fueran cagedráticos.</t>
+  </si>
+  <si>
+    <t>Faltan guías y que estas esten actualizadas.</t>
+  </si>
+  <si>
+    <t>Pueblo Rico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En primaria especialmente.En secundaria parcial </t>
+  </si>
+  <si>
+    <t>Se hace necesario dinamizarlos a nivel municipal como red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No existe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">De manera parcial </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existe proyecto desde el área de sociales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trabajo por áreas, proyectos, microcentro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se solicita actualizar </t>
+  </si>
+  <si>
+    <t>San Luis</t>
+  </si>
+  <si>
+    <t>Se tienen algunos instrumentos. Más en primaria.</t>
+  </si>
+  <si>
+    <t>Se manejan los Microcentros internos, sería bueno volver a los Microcentros municipales.</t>
+  </si>
+  <si>
+    <t>Desde emprendimiento, más NO se tiene capacitación al respecto.</t>
+  </si>
+  <si>
+    <t>Se aplican algunos por falta de capacitación.</t>
+  </si>
+  <si>
+    <t>Tiene su propio proyecto y seguimiento.</t>
+  </si>
+  <si>
+    <t>No se realiza en todas las sedes, ni por todos los docentes.</t>
+  </si>
+  <si>
+    <t>Se intenta pero no es aplicable en todas las sedes ni grupos.</t>
+  </si>
+  <si>
+    <t>Se usan en algunas sedes, asignaturas y NO en todos los ciclos de formación.</t>
+  </si>
+  <si>
+    <t>Pácora</t>
+  </si>
+  <si>
+    <t>La Milagrosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya se cuenta con la ambientación en cada sede y en cada aula de la Institución </t>
+  </si>
+  <si>
+    <t>Se trabaja y esta asignada desde horario general.</t>
+  </si>
+  <si>
+    <t>Se tiene las aulas ambientados atendiendo a los instrumentos del modelo.</t>
+  </si>
+  <si>
+    <t>Se tiene conformado de manera general en la Institución, cada sede dinámica su operatividad de manera constante y sistematizado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se tiene conformado la junta del microcentro donde todos toman en el liderazgo por.vigencias.
+  </t>
+  </si>
+  <si>
+    <t>Se realizan con el manejo de un instrumento diferente cada dia dándole funcionalidad a cada uno.</t>
+  </si>
+  <si>
+    <t>La dinamizacion de trabajo es mancomunado y con relaciones asertivas de interaccion positiva.</t>
+  </si>
+  <si>
+    <t>Se utilizan la específicas y proyectos. En la Institución se construye guías por colectivos de área con la metodología Escuela Nueva.</t>
+  </si>
+  <si>
+    <t>Mariscal Robledo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se asigna un presupuesto para la elaboración de la ambientación de las aulas, ya se estableció un plazo para este aspecto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se cuenta con esta hora dentro del plan de estudios </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se trabajan algunos y se dinamizan desde las actividades de conjunto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existe gobierno estudiantil por aula </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya se eligió la junta, sin embargo estamos a la espera de la circular de sedcaldas  con las fechas autorizadas </t>
+  </si>
+  <si>
+    <t>Se implementa una vez por semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se busca el fortalecimiento del trabajo en equipo de grande las aulas </t>
+  </si>
+  <si>
+    <t>En algunas de las áreas otras se guían por otro tipo de guías diferentes a las entregadas por el modelo pero respetando el modelo</t>
+  </si>
+  <si>
+    <t>Palestina</t>
+  </si>
+  <si>
+    <t>Cartagena</t>
+  </si>
+  <si>
+    <t>se encuentran las aulas ambientadas y se aplican los instrumentos</t>
+  </si>
+  <si>
+    <t>dentro del horario se encuentra establecida para 10 y 11 emprendimiento</t>
+  </si>
+  <si>
+    <t>aplican los instrumentos del gobierno estudiantil</t>
+  </si>
+  <si>
+    <t>está conformado, pero falta operatividad</t>
+  </si>
+  <si>
+    <t>se encuentra conformado la junta directiva de microcentro con fechas de aplicación.</t>
+  </si>
+  <si>
+    <t>dentro del horario se estableció un espacio para las actividades de conjunto.</t>
+  </si>
+  <si>
+    <t>los estudiantes conforman equipos de trabajo para trabajar en el aula</t>
+  </si>
+  <si>
+    <t>presentan adaptaciones de guías bajo el formato establecido por la institución</t>
+  </si>
+  <si>
+    <t>José María Carbonell</t>
+  </si>
+  <si>
+    <t>Las aulas están ambientadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se da en la media. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se utilizan especialmente en las sedes primarias, se deben fortalecer en secundaria </t>
+  </si>
+  <si>
+    <t>Se está trabajando en todas las sedes. Hay espacios especialmente en la sede La Plata,nse debe dinamzar más en las demás sedes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Está organizado, es operativo y hay junta directiva funcionalidad </t>
+  </si>
+  <si>
+    <t>Se hacen pero no diarias. Se acordaron dos días a la semana en el 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Están organizados en mesas hexagonales y trabajan en equipo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se usan las guías y hay adaptaciones </t>
+  </si>
+  <si>
+    <t>Santágueda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aulas ambientadas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se desarrolla como emprendimiento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se sugieren desde la presidencia del modelo 5 instrumentos y los docentes en compañía del grupo los adoptan o cambian según sus necesidades  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza la conformación del gobierno, se hace una plan de trabajo se realizan algunas actividades y otras no por falta de espacios desde las directivas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizan de manera organizada y siguiendo la agenda de secretaría de educación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se hacen en los diferentes grupos y de manera general dentro del cronograma anual </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplica </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se hace uso de las guías existentes, sin embargo faltan guías en diferentes grados, se ha solicitado material sin tener respuesta </t>
+  </si>
+  <si>
+    <t>Pensilvania</t>
+  </si>
+  <si>
+    <t>Daniel María López Rodríguez</t>
+  </si>
+  <si>
+    <t>En cada Aula, incluyendo la Sede Principal estan bien definidos los espacios de Escuela Nueva.</t>
+  </si>
+  <si>
+    <t>El docente comisionado para esta hora la realiza con rigurosidad.</t>
+  </si>
+  <si>
+    <t>Se llevan con rigurisidad.</t>
+  </si>
+  <si>
+    <t>La Institución ha vinculado el Gobierno Estudiantil de cada Escuela Nueva en la articulación del funcionamiento del Gobierno Escolar de la Sede Principal con buenos resultados verificables.</t>
+  </si>
+  <si>
+    <t>Facilita el conocimiento, implementación y evaluación del Modelo.</t>
+  </si>
+  <si>
+    <t>Se realizan utilizando el Back Up de actividades que tiene Pensilvania.</t>
+  </si>
+  <si>
+    <t>Es la base del trabajo, sobre todo en las Escuelas Multigrado.</t>
+  </si>
+  <si>
+    <t>La Institución ha realizado adaptaciones y tiene un material que trabaja con independencia.</t>
+  </si>
+  <si>
+    <t>Guacas</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Funciona en todas la sedes.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Se utilizan pero falta dotación.</t>
+  </si>
+  <si>
+    <t>La Rioja</t>
+  </si>
+  <si>
+    <t>Definidas con los docentes</t>
+  </si>
+  <si>
+    <t>Santa Rita</t>
+  </si>
+  <si>
+    <t>Debe ser más mucho más operativo.</t>
+  </si>
+  <si>
+    <t>Aplicarlos y hacerlos dinámicos en todo el proceso.</t>
+  </si>
+  <si>
+    <t>Debe ser más dinámico tanto el proceso de elección como el trabajo en el año escolar.</t>
+  </si>
+  <si>
+    <t>Deben ser prioridad en la planeación diaria.</t>
+  </si>
+  <si>
+    <t>Hacerlas más dinámicas en el aula.</t>
+  </si>
+  <si>
+    <t>Risaralda</t>
+  </si>
+  <si>
+    <t>Francisco José de Caldas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumentos de aula </t>
+  </si>
+  <si>
+    <t>Se procura realizar los 4 al año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se desarrolla desde 6 con mayor intensidad en la media </t>
+  </si>
+  <si>
+    <t>Autocontrol de asistencia</t>
+  </si>
+  <si>
+    <t>Se implementa y se esta proyectando para seguimiento a los procesos e integracion de sedes</t>
+  </si>
+  <si>
+    <t>Se realizan una cada semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las actividades propuestas en lqsnguuas motivan el trabajo en equipo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se usa material diseñaso por los docentes y las cartillas del comite </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mayoría de las aulas se organizan con los instrumentos , hace falta hacer más énfasis en secundaria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde 4 de primaria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se han definido estrategias institucionales para el uso de los instrumentos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se cumple con todo el proceso </t>
+  </si>
+  <si>
+    <t>Los docentes del equipo de Micro centro han mejorado el proceso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada sede ha definido estrategia para realizar actividades de conjunto. También en reunión de docentes se da espacio para que los docentes realicen actividades de conjunto que pueden ser compartida con los estudiantes </t>
+  </si>
+  <si>
+    <t>Se fortalece en actividades de aula</t>
+  </si>
+  <si>
+    <t>Los docentes elaboran guías de Inter aprendizaje para cada área y periodo</t>
+  </si>
+  <si>
+    <t>Gabriel García Márquez</t>
+  </si>
+  <si>
+    <t>Ninguna por el momento</t>
+  </si>
+  <si>
+    <t>Quiebra de Santa Barbara</t>
+  </si>
+  <si>
+    <t>Se debe fortalecer en secundaria</t>
+  </si>
+  <si>
+    <t>Los hacemos cuando los permiten</t>
+  </si>
+  <si>
+    <t>Se combina con la asignatura de emprendimiento</t>
+  </si>
+  <si>
+    <t>En primaria está fortalecido en secundaria se debe mejorar</t>
+  </si>
+  <si>
+    <t>Se cumple con todas las fases</t>
+  </si>
+  <si>
+    <t>1 vez a la semana las generales, las de aula las debemos fortalecer</t>
+  </si>
+  <si>
+    <t>Se aplica como lo indica el modelo</t>
+  </si>
+  <si>
+    <t>Se aplica en algunas y en otras se adaptan</t>
+  </si>
+  <si>
+    <t>Salamina</t>
+  </si>
+  <si>
+    <t>El Perro</t>
+  </si>
+  <si>
+    <t>Con los instrumentos</t>
+  </si>
+  <si>
+    <t>En Emprendimiento. Se maneja libro de registros.</t>
+  </si>
+  <si>
+    <t>En todas las aulas</t>
+  </si>
+  <si>
+    <t>Con oportunidad de mejora en sede central</t>
+  </si>
+  <si>
+    <t>Junta de microcentro y gestiones</t>
+  </si>
+  <si>
+    <t>En todas las sedes y se dinamizan en los microcentros y semanas de desarrollo institucional</t>
+  </si>
+  <si>
+    <t>Tenemos la junta de microcentro y red de maestros a nivel municipal</t>
+  </si>
+  <si>
+    <t>En las áreas y niveles que se tienen actualizadas.  En todas las áreas de hacen adaptaciones de guías.</t>
+  </si>
+  <si>
+    <t>Luis Felipe Gutiérrez Loaiza</t>
+  </si>
+  <si>
+    <t>Los docentes y los estudiantes se esperan por ambientar sus espacios de aprendizajes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se cuenta en el horario con la asignatura de Emprendimiento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde los microcentros se potencian estrategias para la implementacion de los instrumentos de aula, sin embargo se quiere mayor conciencia y uso pedagógico de los mismos por parte de los.docentes de aula. </t>
+  </si>
+  <si>
+    <t>Algunas sedes requiere mayor acompañamiento en la operatividad del.gobierno estudiantil pues algunos docentes lo confunden con el gobierno escolar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se tiene la junta del microcentro y distribuidos los componentes. Se proyectan los microcentros pensando en la intervención de necesidades de formación institucional y del fortalecimiento del modelo pedagógico </t>
+  </si>
+  <si>
+    <t>En todas las sedes se desarrollan las actividades de conjunto bajo el acompañamiento de los docentes y en los espacios de desarrollo institucional se dinámizan entre docentes y directivos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se tienen establecidos equipos de trabajo de acuerdo a los perfiles docentes, experiencia en proyectos y área de formación. </t>
+  </si>
+  <si>
+    <t>Se hace uso de los textos actualizados entregados por la alianza. Así mismo, los docentes construyen guías de interaprendizaje teniendo en cuenta la secuencia didáctica del modelo.</t>
+  </si>
+  <si>
+    <t>San Félix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se desconoce </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necesidad de capacitación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necesidad de capacitar los docentes por desconocimiento del modelo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se plantean en coordinación con los padrinos del comité de cafeteros </t>
+  </si>
+  <si>
+    <t>Se realizan</t>
+  </si>
+  <si>
+    <t>La disposición del personal es muy buena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algunos docentes son nuevos y no manejan el material </t>
+  </si>
+  <si>
+    <t>Samaná</t>
+  </si>
+  <si>
+    <t>El Silencio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los docentes directores de grupo con sus estudiantes organizan el aula iniciando el año académico , para ofrecer un buen ambiente a los grupos  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se trabaja en la media académica grados 10 y 11 orientada por la docente de Agropecuarias </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se hace el proceso para elección de gobierno estudiantil  en sus fases se nombran los representantes y los comités. 
+Ha </t>
+  </si>
+  <si>
+    <t>Se fortalecen competencias de liderazgo  y se conforman gobierno estudiantil en cada una de las sedes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay docentes líderes de microcentro que velan por la organización y verificación que se realice el plan de acción </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizan actividades de conjunto en acompañamiento del docente . 
+En semana se realiza una actividad de conjunto colectiva institucional  en las sedes de secundaria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existe buena cohesión entre el grupo de docentes, directivos, comunidad para cumplir objetivos  en pro de la institución </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los docentes realizan la planeación ,  diseñan y adaptan las guías de inter aprendizaje.
+Se cuenta con bancos de guías de planeación organizadas por cada docente en todas las áreas   </t>
+  </si>
+  <si>
+    <t>Siempre se trata en la medida de lo posible mejorar los ambientes de aula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se trabaja en los grados 10 y 11, en los otros grados desde preescolar se trabaja como emprendimiento </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necesitamos más acompañamiento en esta estrategia </t>
+  </si>
+  <si>
+    <t>Contamos con el apoyo de la Registraduría municipal</t>
+  </si>
+  <si>
+    <t>Se cuenta con una junta de microcentro muy comprometida</t>
+  </si>
+  <si>
+    <t>Necesitamos más acompañamiemto en esta estrategia</t>
+  </si>
+  <si>
+    <t>La Institución se caracteriza por el trabajo en equipo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se planean las clases con la metodología Escuela Nueva y se tienen en cuenta diferentes fuentes de información. </t>
+  </si>
+  <si>
+    <t>Rancho Largo</t>
+  </si>
+  <si>
+    <t>Se requiere mirar este aspecto y determinar que realmente es funcional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta darle más apoyo a este proceso </t>
+  </si>
+  <si>
+    <t>Se hace, se mira su funcionalidad</t>
+  </si>
+  <si>
+    <t>Es funcional en la mayoría de las sedes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se hizo un buen proceso el año pasado </t>
+  </si>
+  <si>
+    <t>Se está mirando su funcionalidad y como lo están realizando ellas diferentes sedes</t>
+  </si>
+  <si>
+    <t>Es un fuerte del proceso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se hace, pero en muchas áreas se debieron realizar por los docentes </t>
+  </si>
+  <si>
+    <t>San José</t>
+  </si>
+  <si>
+    <t>La Libertad</t>
+  </si>
+  <si>
+    <t>Podemos decir que el 90% de los docentes utilizan estos instrumentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza durante la hora de emprendimiento
+</t>
+  </si>
+  <si>
+    <t>Se realiza cada año la elección del gobierno estudiantil en cada una de las sedes educativas y se hace operativo durante todo el año</t>
+  </si>
+  <si>
+    <t>Se tiene conformada la junta de microcentros y se realizan las actividades según el cronograma establecido por SEDCALDAS</t>
+  </si>
+  <si>
+    <t>Se realiza sobre todo en las escuelas unitarias, y algunos docentes de posprimaria y media</t>
+  </si>
+  <si>
+    <t>Se evidencia y se realiza en todas las actividades institucionales: Comités de área, proyectos transversales, PPT, etc.</t>
+  </si>
+  <si>
+    <t>La mayoría de docentes y sedes han apropiado y hacen uso de las guías sobre todo en las escuelas unitarias. Algunos docentes realizan adaptaciones a aquellas que se encuentran desactualizadas</t>
+  </si>
+  <si>
+    <t>Supía</t>
+  </si>
+  <si>
+    <t>Obispo</t>
+  </si>
+  <si>
+    <t>Si se aplica tanto en primaria como en secundaria de manera adecuada.</t>
+  </si>
+  <si>
+    <t>Se cuenta con la hora de gestión de negocios pero con el nombre Emprendimiento desde grado cuarto.</t>
+  </si>
+  <si>
+    <t>Aplica para las primarias pero en secundaria no se realiza.</t>
+  </si>
+  <si>
+    <t>Existe un gobierno estudiantil de forma general pero no en cada salón tanto en la sede central como en cada sede. Cada aula tiene uno o dos representantes en la sede central.</t>
+  </si>
+  <si>
+    <t>Se cuenta con la junta y componentes organizados para este año.</t>
+  </si>
+  <si>
+    <t>En primaria se hace de manera diariamente. En secundaria se realiza una vez a la semana.</t>
+  </si>
+  <si>
+    <t>Se trabaja de manera adecuada en cada una de las aulas con base a lo que se propone en las guías de interaprendizaje.</t>
+  </si>
+  <si>
+    <t>Se aplica de manera correcta en posprimaria y media. En primaria se elaboran con adaptaciones siguiendo el proceso metodológico del modelo Escuela Nueva.</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>Isaza</t>
+  </si>
+  <si>
+    <t>La ambientación del aula existe</t>
+  </si>
+  <si>
+    <t>Las realizan el profesor de agropecuarias</t>
+  </si>
+  <si>
+    <t>Todas las aulas de las sedes tienen desarrollados tales instrumentos</t>
+  </si>
+  <si>
+    <t>Todos los años se realiza el proceso tal como está establecido y existe un docente que los lidera del PPT de Democracia</t>
+  </si>
+  <si>
+    <t>Se tiene organizada la junta y se realizan 4 mi rocentros al año</t>
+  </si>
+  <si>
+    <t>Se realizan en las 7 sedes anexas. Con el Decretp 0277 sobre jornada laboral y académica, en la sede principal tenemos inconvenientes en realizarlas</t>
+  </si>
+  <si>
+    <t>Existe, se puede evidenciar</t>
+  </si>
+  <si>
+    <t>Se utilizan las guías. Hacen falta pues algunas se han deteriorado y otras se han perdido</t>
+  </si>
+  <si>
+    <t>Villamaría</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Es adecuado y se da armonia para la orientación de las clases.</t>
+  </si>
+  <si>
+    <t>Se está orientando con intansidad horaria semanal</t>
+  </si>
+  <si>
+    <t>Se vienen programando y se aplican en hodas las sedes y grados, se escogen unos instrumenhos y se unifican para su despliegue institucional.</t>
+  </si>
+  <si>
+    <t>Siempre se dan garantias para el protagonismo de los estudiantes en los roles del gobierno estudiantil, sin embargo, sigue faltando más motivación para la participación, tanto para estudiantes como para docentes, mayor dimensionamiento a propósito de los alcances de esta maravilllosa estrategis de participación.</t>
+  </si>
+  <si>
+    <t>Se tiene organizada la planta de personal para el aprovechamiento de los microcentros.</t>
+  </si>
+  <si>
+    <t>Se programan con todos los docentes, se inivia con cumplimiento, algunos docentes, no dsn valor a este momento en las clases.</t>
+  </si>
+  <si>
+    <t>Se ve muy bien el trabajo en equipo, sobretodo en básica primaria, falta fortalecee en secundaria y media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se usan en todis los niveles y grados, pero no en su totalidad, algunos docentes implenentan otras opciones
+</t>
+  </si>
+  <si>
+    <t>Fortunato Gaviria Botero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se hace la debida dotación de implementos que los directores de grupo y sede solicitan para su actualización </t>
+  </si>
+  <si>
+    <t>Se plasma mediante la asignatura de emprendimiento y del énfasis agroindustrial, creando y participando en ferias locales y regionales</t>
+  </si>
+  <si>
+    <t>Se implementan de acuerdo al cronograma anual de elección del gobierno estudiantil y de las reuniones periódicas para su seguimiento.</t>
+  </si>
+  <si>
+    <t>Se requiere capacitar al gobierno estudiantil a través de visitas por parte del Comité, en alianza con entidades tales como la personería, contraloría y afines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La líder institucional de la Red de Maestros con el acompañamiento del padrino David han hecho con suficiencia sensibilización a docentes sobre aspectos del Modelo Pedagógico Escuela Nueva.n </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se requiere fortalecer en la postprimaria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se evidencia en espacios tales como las jornadas de desarrollo institucional, microcentros, jornadas deportivas, entre otros escenarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se requiere que el enfoque sea de producción lúdico - didáctica más que la tradicionalmente bibliográfica mediante guías </t>
+  </si>
+  <si>
+    <t>Partidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As e tienen ambientes de aprendizaje requeridos por los procesos institucionales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se tiene asignada en el horario institucional </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se tienen los básicos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Está en proceso de elección </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se dan los cuatro y se dan acuerdos mediante acta y seguimiento yo a los mismos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se desarrollan teniendo presente los espacios acordados institucionalmente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algunos docentes no trabajan con el modelo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se hace adaptación de guías y algunos no utilizan el modelo porque están desactualizaras y tienen problemas de salubridad </t>
+  </si>
+  <si>
+    <t>Fortalecerlos</t>
+  </si>
+  <si>
+    <t>Existe en el horario</t>
+  </si>
+  <si>
+    <t>Son operativos</t>
+  </si>
+  <si>
+    <t>Fortalecerlo</t>
+  </si>
+  <si>
+    <t>Estan organizados</t>
+  </si>
+  <si>
+    <t>De ejecutsn</t>
+  </si>
+  <si>
+    <t>Estan orgsnizados</t>
+  </si>
+  <si>
+    <t>Actualizarlas</t>
+  </si>
+  <si>
+    <t>Viterbo</t>
+  </si>
+  <si>
+    <t>El Socorro</t>
+  </si>
+  <si>
+    <t>Parcialmente, porque no todos los profesores lo hacen.</t>
+  </si>
+  <si>
+    <t>Sí, desde la transversalizacion con emprendimiento.</t>
+  </si>
+  <si>
+    <t>Falta compromiso de los profesores en este proceso.</t>
+  </si>
+  <si>
+    <t>Se conforma y cumple con sus funciones en la sede central y en las anexas.</t>
+  </si>
+  <si>
+    <t>Se conforman los comités y se realizan los microcentros.</t>
+  </si>
+  <si>
+    <t>Sí, todos los profesores en sus diferentes asignaturas.</t>
+  </si>
+  <si>
+    <t>Se trabaja en equipo.</t>
+  </si>
+  <si>
+    <t>Se implementan con el acompañamiento del padrino y el trabajo de los docentes.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -516,9 +2291,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U70"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -543,7 +2318,7 @@
     <col min="21" max="21" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -608,138 +2383,4493 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>41</v>
+      </c>
+      <c r="R3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>50</v>
+      </c>
+      <c r="R4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T4" t="s">
+        <v>24</v>
+      </c>
+      <c r="U4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>58</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>59</v>
+      </c>
+      <c r="R5" t="s">
+        <v>24</v>
+      </c>
+      <c r="S5" t="s">
+        <v>60</v>
+      </c>
+      <c r="T5" t="s">
+        <v>24</v>
+      </c>
+      <c r="U5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>68</v>
+      </c>
+      <c r="R6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S6" t="s">
+        <v>69</v>
+      </c>
+      <c r="T6" t="s">
+        <v>24</v>
+      </c>
+      <c r="U6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
+        <v>75</v>
+      </c>
+      <c r="L7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S7" t="s">
+        <v>78</v>
+      </c>
+      <c r="T7" t="s">
+        <v>24</v>
+      </c>
+      <c r="U7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" t="s">
+        <v>86</v>
+      </c>
+      <c r="N8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" t="s">
+        <v>24</v>
+      </c>
+      <c r="S8" t="s">
+        <v>88</v>
+      </c>
+      <c r="T8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" t="s">
-        <v>22</v>
-      </c>
-      <c r="U2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="K9" t="s">
+        <v>94</v>
+      </c>
+      <c r="L9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" t="s">
+        <v>95</v>
+      </c>
+      <c r="N9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>94</v>
+      </c>
+      <c r="R9" t="s">
+        <v>24</v>
+      </c>
+      <c r="S9" t="s">
+        <v>96</v>
+      </c>
+      <c r="T9" t="s">
+        <v>24</v>
+      </c>
+      <c r="U9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O10" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>102</v>
+      </c>
+      <c r="R10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S10" t="s">
+        <v>99</v>
+      </c>
+      <c r="T10" t="s">
+        <v>24</v>
+      </c>
+      <c r="U10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
+        <v>106</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
+        <v>107</v>
+      </c>
+      <c r="L11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" t="s">
+        <v>108</v>
+      </c>
+      <c r="N11" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P11" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>109</v>
+      </c>
+      <c r="R11" t="s">
+        <v>24</v>
+      </c>
+      <c r="S11" t="s">
+        <v>110</v>
+      </c>
+      <c r="T11" t="s">
+        <v>24</v>
+      </c>
+      <c r="U11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" t="s">
+        <v>116</v>
+      </c>
+      <c r="L12" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" t="s">
+        <v>117</v>
+      </c>
+      <c r="N12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O12" t="s">
+        <v>31</v>
+      </c>
+      <c r="P12" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>118</v>
+      </c>
+      <c r="R12" t="s">
+        <v>24</v>
+      </c>
+      <c r="S12" t="s">
+        <v>119</v>
+      </c>
+      <c r="T12" t="s">
+        <v>24</v>
+      </c>
+      <c r="U12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>124</v>
+      </c>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" t="s">
+        <v>125</v>
+      </c>
+      <c r="L13" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" t="s">
+        <v>126</v>
+      </c>
+      <c r="N13" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" t="s">
+        <v>127</v>
+      </c>
+      <c r="P13" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>128</v>
+      </c>
+      <c r="R13" t="s">
+        <v>24</v>
+      </c>
+      <c r="S13" t="s">
+        <v>129</v>
+      </c>
+      <c r="T13" t="s">
+        <v>24</v>
+      </c>
+      <c r="U13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" t="s">
+        <v>133</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s">
+        <v>134</v>
+      </c>
+      <c r="J14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" t="s">
+        <v>135</v>
+      </c>
+      <c r="L14" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" t="s">
+        <v>136</v>
+      </c>
+      <c r="N14" t="s">
+        <v>31</v>
+      </c>
+      <c r="O14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>137</v>
+      </c>
+      <c r="R14" t="s">
+        <v>24</v>
+      </c>
+      <c r="S14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T14" t="s">
+        <v>24</v>
+      </c>
+      <c r="U14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>141</v>
+      </c>
+      <c r="F15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" t="s">
+        <v>143</v>
+      </c>
+      <c r="L15" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" t="s">
+        <v>144</v>
+      </c>
+      <c r="N15" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" t="s">
+        <v>99</v>
+      </c>
+      <c r="P15" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>145</v>
+      </c>
+      <c r="R15" t="s">
+        <v>24</v>
+      </c>
+      <c r="S15" t="s">
+        <v>146</v>
+      </c>
+      <c r="T15" t="s">
+        <v>24</v>
+      </c>
+      <c r="U15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
+        <v>151</v>
+      </c>
+      <c r="J16" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" t="s">
+        <v>152</v>
+      </c>
+      <c r="L16" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" t="s">
+        <v>153</v>
+      </c>
+      <c r="N16" t="s">
+        <v>24</v>
+      </c>
+      <c r="O16" t="s">
+        <v>154</v>
+      </c>
+      <c r="P16" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>155</v>
+      </c>
+      <c r="R16" t="s">
+        <v>24</v>
+      </c>
+      <c r="S16" t="s">
+        <v>156</v>
+      </c>
+      <c r="T16" t="s">
+        <v>24</v>
+      </c>
+      <c r="U16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" t="s">
+        <v>160</v>
+      </c>
+      <c r="J17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" t="s">
+        <v>161</v>
+      </c>
+      <c r="L17" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" t="s">
+        <v>162</v>
+      </c>
+      <c r="N17" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" t="s">
+        <v>163</v>
+      </c>
+      <c r="P17" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>162</v>
+      </c>
+      <c r="R17" t="s">
+        <v>24</v>
+      </c>
+      <c r="S17" t="s">
+        <v>164</v>
+      </c>
+      <c r="T17" t="s">
+        <v>24</v>
+      </c>
+      <c r="U17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" t="s">
+        <v>168</v>
+      </c>
+      <c r="J18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" t="s">
+        <v>169</v>
+      </c>
+      <c r="L18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" t="s">
+        <v>170</v>
+      </c>
+      <c r="N18" t="s">
+        <v>24</v>
+      </c>
+      <c r="O18" t="s">
+        <v>171</v>
+      </c>
+      <c r="P18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>172</v>
+      </c>
+      <c r="R18" t="s">
+        <v>24</v>
+      </c>
+      <c r="S18" t="s">
+        <v>173</v>
+      </c>
+      <c r="T18" t="s">
+        <v>24</v>
+      </c>
+      <c r="U18" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
+        <v>177</v>
+      </c>
+      <c r="F19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" t="s">
+        <v>178</v>
+      </c>
+      <c r="J19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" t="s">
+        <v>179</v>
+      </c>
+      <c r="L19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" t="s">
+        <v>180</v>
+      </c>
+      <c r="N19" t="s">
+        <v>24</v>
+      </c>
+      <c r="O19" t="s">
+        <v>181</v>
+      </c>
+      <c r="P19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>182</v>
+      </c>
+      <c r="R19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" t="s">
+        <v>183</v>
+      </c>
+      <c r="T19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>185</v>
+      </c>
+      <c r="B20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
+        <v>187</v>
+      </c>
+      <c r="F20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" t="s">
+        <v>188</v>
+      </c>
+      <c r="J20" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" t="s">
+        <v>189</v>
+      </c>
+      <c r="L20" t="s">
+        <v>24</v>
+      </c>
+      <c r="M20" t="s">
+        <v>190</v>
+      </c>
+      <c r="N20" t="s">
+        <v>24</v>
+      </c>
+      <c r="O20" t="s">
+        <v>191</v>
+      </c>
+      <c r="P20" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>192</v>
+      </c>
+      <c r="R20" t="s">
+        <v>24</v>
+      </c>
+      <c r="S20" t="s">
+        <v>193</v>
+      </c>
+      <c r="T20" t="s">
+        <v>24</v>
+      </c>
+      <c r="U20" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
+        <v>196</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" t="s">
+        <v>197</v>
+      </c>
+      <c r="J21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" t="s">
+        <v>198</v>
+      </c>
+      <c r="L21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" t="s">
+        <v>199</v>
+      </c>
+      <c r="N21" t="s">
+        <v>24</v>
+      </c>
+      <c r="O21" t="s">
+        <v>200</v>
+      </c>
+      <c r="P21" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>201</v>
+      </c>
+      <c r="R21" t="s">
+        <v>24</v>
+      </c>
+      <c r="S21" t="s">
+        <v>202</v>
+      </c>
+      <c r="T21" t="s">
+        <v>24</v>
+      </c>
+      <c r="U21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>204</v>
+      </c>
+      <c r="B22" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
+        <v>206</v>
+      </c>
+      <c r="F22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" t="s">
+        <v>207</v>
+      </c>
+      <c r="J22" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" t="s">
+        <v>208</v>
+      </c>
+      <c r="L22" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" t="s">
+        <v>209</v>
+      </c>
+      <c r="N22" t="s">
+        <v>24</v>
+      </c>
+      <c r="O22" t="s">
+        <v>210</v>
+      </c>
+      <c r="P22" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>211</v>
+      </c>
+      <c r="R22" t="s">
+        <v>24</v>
+      </c>
+      <c r="S22" t="s">
+        <v>212</v>
+      </c>
+      <c r="T22" t="s">
+        <v>24</v>
+      </c>
+      <c r="U22" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>204</v>
+      </c>
+      <c r="B23" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>215</v>
+      </c>
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" t="s">
+        <v>216</v>
+      </c>
+      <c r="J23" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" t="s">
+        <v>217</v>
+      </c>
+      <c r="L23" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" t="s">
+        <v>218</v>
+      </c>
+      <c r="N23" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" t="s">
+        <v>219</v>
+      </c>
+      <c r="P23" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>220</v>
+      </c>
+      <c r="R23" t="s">
+        <v>24</v>
+      </c>
+      <c r="S23" t="s">
+        <v>221</v>
+      </c>
+      <c r="T23" t="s">
+        <v>24</v>
+      </c>
+      <c r="U23" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>223</v>
+      </c>
+      <c r="B24" t="s">
+        <v>224</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>225</v>
+      </c>
+      <c r="F24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" t="s">
+        <v>226</v>
+      </c>
+      <c r="J24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" t="s">
+        <v>227</v>
+      </c>
+      <c r="L24" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" t="s">
+        <v>228</v>
+      </c>
+      <c r="N24" t="s">
+        <v>24</v>
+      </c>
+      <c r="O24" t="s">
+        <v>229</v>
+      </c>
+      <c r="P24" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>230</v>
+      </c>
+      <c r="R24" t="s">
+        <v>24</v>
+      </c>
+      <c r="S24" t="s">
+        <v>231</v>
+      </c>
+      <c r="T24" t="s">
+        <v>24</v>
+      </c>
+      <c r="U24" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>223</v>
+      </c>
+      <c r="B25" t="s">
+        <v>224</v>
+      </c>
+      <c r="C25" t="s">
+        <v>176</v>
+      </c>
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" t="s">
+        <v>233</v>
+      </c>
+      <c r="F25" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" t="s">
+        <v>234</v>
+      </c>
+      <c r="J25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" t="s">
+        <v>235</v>
+      </c>
+      <c r="L25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M25" t="s">
+        <v>236</v>
+      </c>
+      <c r="N25" t="s">
+        <v>24</v>
+      </c>
+      <c r="O25" t="s">
+        <v>237</v>
+      </c>
+      <c r="P25" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>238</v>
+      </c>
+      <c r="R25" t="s">
+        <v>27</v>
+      </c>
+      <c r="S25" t="s">
+        <v>239</v>
+      </c>
+      <c r="T25" t="s">
+        <v>27</v>
+      </c>
+      <c r="U25" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>241</v>
+      </c>
+      <c r="B26" t="s">
+        <v>242</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" t="s">
+        <v>243</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" t="s">
+        <v>244</v>
+      </c>
+      <c r="J26" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" t="s">
+        <v>245</v>
+      </c>
+      <c r="L26" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" t="s">
+        <v>246</v>
+      </c>
+      <c r="N26" t="s">
+        <v>24</v>
+      </c>
+      <c r="O26" t="s">
+        <v>247</v>
+      </c>
+      <c r="P26" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>248</v>
+      </c>
+      <c r="R26" t="s">
+        <v>24</v>
+      </c>
+      <c r="S26" t="s">
+        <v>249</v>
+      </c>
+      <c r="T26" t="s">
+        <v>24</v>
+      </c>
+      <c r="U26" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>241</v>
+      </c>
+      <c r="B27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" t="s">
+        <v>252</v>
+      </c>
+      <c r="F27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" t="s">
+        <v>253</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" t="s">
+        <v>254</v>
+      </c>
+      <c r="J27" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" t="s">
+        <v>255</v>
+      </c>
+      <c r="L27" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" t="s">
+        <v>256</v>
+      </c>
+      <c r="N27" t="s">
+        <v>31</v>
+      </c>
+      <c r="O27" t="s">
+        <v>31</v>
+      </c>
+      <c r="P27" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>257</v>
+      </c>
+      <c r="R27" t="s">
+        <v>24</v>
+      </c>
+      <c r="S27" t="s">
+        <v>258</v>
+      </c>
+      <c r="T27" t="s">
+        <v>24</v>
+      </c>
+      <c r="U27" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>241</v>
+      </c>
+      <c r="B28" t="s">
+        <v>260</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" t="s">
+        <v>261</v>
+      </c>
+      <c r="F28" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" t="s">
+        <v>262</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" t="s">
+        <v>263</v>
+      </c>
+      <c r="J28" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" t="s">
+        <v>264</v>
+      </c>
+      <c r="L28" t="s">
+        <v>24</v>
+      </c>
+      <c r="M28" t="s">
+        <v>265</v>
+      </c>
+      <c r="N28" t="s">
+        <v>31</v>
+      </c>
+      <c r="O28" t="s">
+        <v>31</v>
+      </c>
+      <c r="P28" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>266</v>
+      </c>
+      <c r="R28" t="s">
+        <v>24</v>
+      </c>
+      <c r="S28" t="s">
+        <v>267</v>
+      </c>
+      <c r="T28" t="s">
+        <v>24</v>
+      </c>
+      <c r="U28" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>241</v>
+      </c>
+      <c r="B29" t="s">
+        <v>269</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" t="s">
+        <v>270</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" t="s">
+        <v>271</v>
+      </c>
+      <c r="J29" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" t="s">
+        <v>272</v>
+      </c>
+      <c r="L29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M29" t="s">
+        <v>273</v>
+      </c>
+      <c r="N29" t="s">
+        <v>24</v>
+      </c>
+      <c r="O29" t="s">
+        <v>274</v>
+      </c>
+      <c r="P29" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>275</v>
+      </c>
+      <c r="R29" t="s">
+        <v>27</v>
+      </c>
+      <c r="S29" t="s">
+        <v>276</v>
+      </c>
+      <c r="T29" t="s">
+        <v>24</v>
+      </c>
+      <c r="U29" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>278</v>
+      </c>
+      <c r="B30" t="s">
+        <v>279</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" t="s">
+        <v>280</v>
+      </c>
+      <c r="F30" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" t="s">
+        <v>281</v>
+      </c>
+      <c r="J30" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" t="s">
+        <v>282</v>
+      </c>
+      <c r="L30" t="s">
+        <v>24</v>
+      </c>
+      <c r="M30" t="s">
+        <v>283</v>
+      </c>
+      <c r="N30" t="s">
+        <v>24</v>
+      </c>
+      <c r="O30" t="s">
+        <v>284</v>
+      </c>
+      <c r="P30" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>285</v>
+      </c>
+      <c r="R30" t="s">
+        <v>24</v>
+      </c>
+      <c r="S30" t="s">
+        <v>286</v>
+      </c>
+      <c r="T30" t="s">
+        <v>27</v>
+      </c>
+      <c r="U30" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>278</v>
+      </c>
+      <c r="B31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" t="s">
+        <v>289</v>
+      </c>
+      <c r="F31" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" t="s">
+        <v>290</v>
+      </c>
+      <c r="J31" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" t="s">
+        <v>291</v>
+      </c>
+      <c r="L31" t="s">
+        <v>24</v>
+      </c>
+      <c r="M31" t="s">
+        <v>292</v>
+      </c>
+      <c r="N31" t="s">
+        <v>24</v>
+      </c>
+      <c r="O31" t="s">
+        <v>293</v>
+      </c>
+      <c r="P31" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>294</v>
+      </c>
+      <c r="R31" t="s">
+        <v>24</v>
+      </c>
+      <c r="S31" t="s">
+        <v>295</v>
+      </c>
+      <c r="T31" t="s">
+        <v>24</v>
+      </c>
+      <c r="U31" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>278</v>
+      </c>
+      <c r="B32" t="s">
+        <v>297</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" t="s">
+        <v>298</v>
+      </c>
+      <c r="F32" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" t="s">
+        <v>299</v>
+      </c>
+      <c r="J32" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" t="s">
+        <v>300</v>
+      </c>
+      <c r="L32" t="s">
+        <v>24</v>
+      </c>
+      <c r="M32" t="s">
+        <v>301</v>
+      </c>
+      <c r="N32" t="s">
+        <v>24</v>
+      </c>
+      <c r="O32" t="s">
+        <v>302</v>
+      </c>
+      <c r="P32" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>303</v>
+      </c>
+      <c r="R32" t="s">
+        <v>24</v>
+      </c>
+      <c r="S32" t="s">
+        <v>304</v>
+      </c>
+      <c r="T32" t="s">
+        <v>24</v>
+      </c>
+      <c r="U32" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>278</v>
+      </c>
+      <c r="B33" t="s">
+        <v>278</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" t="s">
+        <v>306</v>
+      </c>
+      <c r="F33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" t="s">
+        <v>307</v>
+      </c>
+      <c r="J33" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" t="s">
+        <v>308</v>
+      </c>
+      <c r="L33" t="s">
+        <v>24</v>
+      </c>
+      <c r="M33" t="s">
+        <v>309</v>
+      </c>
+      <c r="N33" t="s">
+        <v>24</v>
+      </c>
+      <c r="O33" t="s">
+        <v>310</v>
+      </c>
+      <c r="P33" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>311</v>
+      </c>
+      <c r="R33" t="s">
+        <v>24</v>
+      </c>
+      <c r="S33" t="s">
+        <v>312</v>
+      </c>
+      <c r="T33" t="s">
+        <v>24</v>
+      </c>
+      <c r="U33" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B34" t="s">
+        <v>314</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" t="s">
+        <v>315</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" t="s">
+        <v>316</v>
+      </c>
+      <c r="J34" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" t="s">
+        <v>317</v>
+      </c>
+      <c r="L34" t="s">
+        <v>24</v>
+      </c>
+      <c r="M34" t="s">
+        <v>318</v>
+      </c>
+      <c r="N34" t="s">
+        <v>24</v>
+      </c>
+      <c r="O34" t="s">
+        <v>319</v>
+      </c>
+      <c r="P34" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>320</v>
+      </c>
+      <c r="R34" t="s">
+        <v>24</v>
+      </c>
+      <c r="S34" t="s">
+        <v>321</v>
+      </c>
+      <c r="T34" t="s">
+        <v>24</v>
+      </c>
+      <c r="U34" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>323</v>
+      </c>
+      <c r="B35" t="s">
+        <v>324</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" t="s">
+        <v>325</v>
+      </c>
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" t="s">
+        <v>326</v>
+      </c>
+      <c r="J35" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" t="s">
+        <v>327</v>
+      </c>
+      <c r="L35" t="s">
+        <v>24</v>
+      </c>
+      <c r="M35" t="s">
+        <v>328</v>
+      </c>
+      <c r="N35" t="s">
+        <v>24</v>
+      </c>
+      <c r="O35" t="s">
+        <v>329</v>
+      </c>
+      <c r="P35" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>330</v>
+      </c>
+      <c r="R35" t="s">
+        <v>24</v>
+      </c>
+      <c r="S35" t="s">
+        <v>331</v>
+      </c>
+      <c r="T35" t="s">
+        <v>24</v>
+      </c>
+      <c r="U35" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>323</v>
+      </c>
+      <c r="B36" t="s">
+        <v>333</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" t="s">
+        <v>334</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" t="s">
+        <v>335</v>
+      </c>
+      <c r="J36" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" t="s">
+        <v>336</v>
+      </c>
+      <c r="L36" t="s">
+        <v>24</v>
+      </c>
+      <c r="M36" t="s">
+        <v>337</v>
+      </c>
+      <c r="N36" t="s">
+        <v>24</v>
+      </c>
+      <c r="O36" t="s">
+        <v>338</v>
+      </c>
+      <c r="P36" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>339</v>
+      </c>
+      <c r="R36" t="s">
+        <v>24</v>
+      </c>
+      <c r="S36" t="s">
+        <v>340</v>
+      </c>
+      <c r="T36" t="s">
+        <v>24</v>
+      </c>
+      <c r="U36" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>323</v>
+      </c>
+      <c r="B37" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" t="s">
+        <v>343</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" t="s">
+        <v>344</v>
+      </c>
+      <c r="J37" t="s">
+        <v>24</v>
+      </c>
+      <c r="K37" t="s">
+        <v>345</v>
+      </c>
+      <c r="L37" t="s">
+        <v>24</v>
+      </c>
+      <c r="M37" t="s">
+        <v>346</v>
+      </c>
+      <c r="N37" t="s">
+        <v>24</v>
+      </c>
+      <c r="O37" t="s">
+        <v>347</v>
+      </c>
+      <c r="P37" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>345</v>
+      </c>
+      <c r="R37" t="s">
+        <v>24</v>
+      </c>
+      <c r="S37" t="s">
+        <v>348</v>
+      </c>
+      <c r="T37" t="s">
+        <v>24</v>
+      </c>
+      <c r="U37" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>323</v>
+      </c>
+      <c r="B38" t="s">
+        <v>350</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" t="s">
+        <v>351</v>
+      </c>
+      <c r="F38" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" t="s">
+        <v>352</v>
+      </c>
+      <c r="J38" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" t="s">
+        <v>353</v>
+      </c>
+      <c r="L38" t="s">
+        <v>24</v>
+      </c>
+      <c r="M38" t="s">
+        <v>354</v>
+      </c>
+      <c r="N38" t="s">
+        <v>24</v>
+      </c>
+      <c r="O38" t="s">
+        <v>355</v>
+      </c>
+      <c r="P38" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>356</v>
+      </c>
+      <c r="R38" t="s">
+        <v>24</v>
+      </c>
+      <c r="S38" t="s">
+        <v>357</v>
+      </c>
+      <c r="T38" t="s">
+        <v>24</v>
+      </c>
+      <c r="U38" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>359</v>
+      </c>
+      <c r="B39" t="s">
+        <v>360</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" t="s">
+        <v>361</v>
+      </c>
+      <c r="F39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" t="s">
+        <v>362</v>
+      </c>
+      <c r="H39" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" t="s">
+        <v>363</v>
+      </c>
+      <c r="J39" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" t="s">
+        <v>364</v>
+      </c>
+      <c r="L39" t="s">
+        <v>24</v>
+      </c>
+      <c r="M39" t="s">
+        <v>365</v>
+      </c>
+      <c r="N39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O39" t="s">
+        <v>31</v>
+      </c>
+      <c r="P39" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>366</v>
+      </c>
+      <c r="R39" t="s">
+        <v>24</v>
+      </c>
+      <c r="S39" t="s">
+        <v>367</v>
+      </c>
+      <c r="T39" t="s">
+        <v>24</v>
+      </c>
+      <c r="U39" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>359</v>
+      </c>
+      <c r="B40" t="s">
+        <v>369</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" t="s">
+        <v>370</v>
+      </c>
+      <c r="F40" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" t="s">
+        <v>371</v>
+      </c>
+      <c r="H40" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" t="s">
+        <v>372</v>
+      </c>
+      <c r="J40" t="s">
+        <v>24</v>
+      </c>
+      <c r="K40" t="s">
+        <v>373</v>
+      </c>
+      <c r="L40" t="s">
+        <v>24</v>
+      </c>
+      <c r="M40" t="s">
+        <v>374</v>
+      </c>
+      <c r="N40" t="s">
+        <v>31</v>
+      </c>
+      <c r="O40" t="s">
+        <v>31</v>
+      </c>
+      <c r="P40" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>373</v>
+      </c>
+      <c r="R40" t="s">
+        <v>24</v>
+      </c>
+      <c r="S40" t="s">
+        <v>375</v>
+      </c>
+      <c r="T40" t="s">
+        <v>24</v>
+      </c>
+      <c r="U40" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>359</v>
+      </c>
+      <c r="B41" t="s">
+        <v>376</v>
+      </c>
+      <c r="C41" t="s">
+        <v>377</v>
+      </c>
+      <c r="D41" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" t="s">
+        <v>378</v>
+      </c>
+      <c r="F41" t="s">
+        <v>24</v>
+      </c>
+      <c r="G41" t="s">
+        <v>379</v>
+      </c>
+      <c r="H41" t="s">
+        <v>27</v>
+      </c>
+      <c r="I41" t="s">
+        <v>380</v>
+      </c>
+      <c r="J41" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" t="s">
+        <v>381</v>
+      </c>
+      <c r="L41" t="s">
+        <v>24</v>
+      </c>
+      <c r="M41" t="s">
+        <v>382</v>
+      </c>
+      <c r="N41" t="s">
+        <v>31</v>
+      </c>
+      <c r="O41" t="s">
+        <v>31</v>
+      </c>
+      <c r="P41" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>383</v>
+      </c>
+      <c r="R41" t="s">
+        <v>27</v>
+      </c>
+      <c r="S41" t="s">
+        <v>384</v>
+      </c>
+      <c r="T41" t="s">
+        <v>24</v>
+      </c>
+      <c r="U41" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>359</v>
+      </c>
+      <c r="B42" t="s">
+        <v>386</v>
+      </c>
+      <c r="C42" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" t="s">
+        <v>387</v>
+      </c>
+      <c r="F42" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" t="s">
+        <v>388</v>
+      </c>
+      <c r="H42" t="s">
+        <v>27</v>
+      </c>
+      <c r="I42" t="s">
+        <v>389</v>
+      </c>
+      <c r="J42" t="s">
+        <v>24</v>
+      </c>
+      <c r="K42" t="s">
+        <v>390</v>
+      </c>
+      <c r="L42" t="s">
+        <v>24</v>
+      </c>
+      <c r="M42" t="s">
+        <v>391</v>
+      </c>
+      <c r="N42" t="s">
+        <v>31</v>
+      </c>
+      <c r="O42" t="s">
+        <v>31</v>
+      </c>
+      <c r="P42" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>289</v>
+      </c>
+      <c r="R42" t="s">
+        <v>24</v>
+      </c>
+      <c r="S42" t="s">
+        <v>392</v>
+      </c>
+      <c r="T42" t="s">
+        <v>24</v>
+      </c>
+      <c r="U42" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>359</v>
+      </c>
+      <c r="B43" t="s">
+        <v>394</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" t="s">
+        <v>395</v>
+      </c>
+      <c r="F43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" t="s">
+        <v>396</v>
+      </c>
+      <c r="H43" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43" t="s">
+        <v>397</v>
+      </c>
+      <c r="J43" t="s">
+        <v>24</v>
+      </c>
+      <c r="K43" t="s">
+        <v>398</v>
+      </c>
+      <c r="L43" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" t="s">
+        <v>399</v>
+      </c>
+      <c r="N43" t="s">
+        <v>31</v>
+      </c>
+      <c r="O43" t="s">
+        <v>31</v>
+      </c>
+      <c r="P43" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>400</v>
+      </c>
+      <c r="R43" t="s">
+        <v>24</v>
+      </c>
+      <c r="S43" t="s">
+        <v>401</v>
+      </c>
+      <c r="T43" t="s">
+        <v>24</v>
+      </c>
+      <c r="U43" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>403</v>
+      </c>
+      <c r="B44" t="s">
+        <v>404</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" t="s">
+        <v>405</v>
+      </c>
+      <c r="F44" t="s">
+        <v>31</v>
+      </c>
+      <c r="G44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" t="s">
+        <v>406</v>
+      </c>
+      <c r="J44" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" t="s">
+        <v>407</v>
+      </c>
+      <c r="L44" t="s">
+        <v>24</v>
+      </c>
+      <c r="M44" t="s">
+        <v>408</v>
+      </c>
+      <c r="N44" t="s">
+        <v>24</v>
+      </c>
+      <c r="O44" t="s">
+        <v>409</v>
+      </c>
+      <c r="P44" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>410</v>
+      </c>
+      <c r="R44" t="s">
+        <v>24</v>
+      </c>
+      <c r="S44" t="s">
+        <v>411</v>
+      </c>
+      <c r="T44" t="s">
+        <v>24</v>
+      </c>
+      <c r="U44" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>403</v>
+      </c>
+      <c r="B45" t="s">
+        <v>413</v>
+      </c>
+      <c r="C45" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" t="s">
+        <v>414</v>
+      </c>
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" t="s">
+        <v>415</v>
+      </c>
+      <c r="J45" t="s">
+        <v>24</v>
+      </c>
+      <c r="K45" t="s">
+        <v>416</v>
+      </c>
+      <c r="L45" t="s">
+        <v>24</v>
+      </c>
+      <c r="M45" t="s">
+        <v>417</v>
+      </c>
+      <c r="N45" t="s">
+        <v>24</v>
+      </c>
+      <c r="O45" t="s">
+        <v>418</v>
+      </c>
+      <c r="P45" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>419</v>
+      </c>
+      <c r="R45" t="s">
+        <v>24</v>
+      </c>
+      <c r="S45" t="s">
+        <v>420</v>
+      </c>
+      <c r="T45" t="s">
+        <v>24</v>
+      </c>
+      <c r="U45" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>422</v>
+      </c>
+      <c r="B46" t="s">
+        <v>423</v>
+      </c>
+      <c r="C46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" t="s">
+        <v>424</v>
+      </c>
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" t="s">
+        <v>31</v>
+      </c>
+      <c r="H46" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" t="s">
+        <v>425</v>
+      </c>
+      <c r="J46" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" t="s">
+        <v>426</v>
+      </c>
+      <c r="L46" t="s">
+        <v>24</v>
+      </c>
+      <c r="M46" t="s">
+        <v>427</v>
+      </c>
+      <c r="N46" t="s">
+        <v>24</v>
+      </c>
+      <c r="O46" t="s">
+        <v>428</v>
+      </c>
+      <c r="P46" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>429</v>
+      </c>
+      <c r="R46" t="s">
+        <v>24</v>
+      </c>
+      <c r="S46" t="s">
+        <v>430</v>
+      </c>
+      <c r="T46" t="s">
+        <v>24</v>
+      </c>
+      <c r="U46" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>422</v>
+      </c>
+      <c r="B47" t="s">
+        <v>432</v>
+      </c>
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" t="s">
+        <v>433</v>
+      </c>
+      <c r="F47" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" t="s">
+        <v>31</v>
+      </c>
+      <c r="H47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" t="s">
+        <v>434</v>
+      </c>
+      <c r="J47" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" t="s">
+        <v>435</v>
+      </c>
+      <c r="L47" t="s">
+        <v>24</v>
+      </c>
+      <c r="M47" t="s">
+        <v>436</v>
+      </c>
+      <c r="N47" t="s">
+        <v>24</v>
+      </c>
+      <c r="O47" t="s">
+        <v>437</v>
+      </c>
+      <c r="P47" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>438</v>
+      </c>
+      <c r="R47" t="s">
+        <v>24</v>
+      </c>
+      <c r="S47" t="s">
+        <v>439</v>
+      </c>
+      <c r="T47" t="s">
+        <v>24</v>
+      </c>
+      <c r="U47" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>422</v>
+      </c>
+      <c r="B48" t="s">
+        <v>441</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" t="s">
+        <v>442</v>
+      </c>
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" t="s">
+        <v>443</v>
+      </c>
+      <c r="J48" t="s">
+        <v>24</v>
+      </c>
+      <c r="K48" t="s">
+        <v>444</v>
+      </c>
+      <c r="L48" t="s">
+        <v>24</v>
+      </c>
+      <c r="M48" t="s">
+        <v>445</v>
+      </c>
+      <c r="N48" t="s">
+        <v>24</v>
+      </c>
+      <c r="O48" t="s">
+        <v>446</v>
+      </c>
+      <c r="P48" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>447</v>
+      </c>
+      <c r="R48" t="s">
+        <v>24</v>
+      </c>
+      <c r="S48" t="s">
+        <v>448</v>
+      </c>
+      <c r="T48" t="s">
+        <v>24</v>
+      </c>
+      <c r="U48" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>450</v>
+      </c>
+      <c r="B49" t="s">
+        <v>451</v>
+      </c>
+      <c r="C49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" t="s">
+        <v>452</v>
+      </c>
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49" t="s">
+        <v>453</v>
+      </c>
+      <c r="J49" t="s">
+        <v>24</v>
+      </c>
+      <c r="K49" t="s">
+        <v>454</v>
+      </c>
+      <c r="L49" t="s">
+        <v>24</v>
+      </c>
+      <c r="M49" t="s">
+        <v>455</v>
+      </c>
+      <c r="N49" t="s">
+        <v>24</v>
+      </c>
+      <c r="O49" t="s">
+        <v>456</v>
+      </c>
+      <c r="P49" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>457</v>
+      </c>
+      <c r="R49" t="s">
+        <v>24</v>
+      </c>
+      <c r="S49" t="s">
+        <v>458</v>
+      </c>
+      <c r="T49" t="s">
+        <v>27</v>
+      </c>
+      <c r="U49" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>450</v>
+      </c>
+      <c r="B50" t="s">
+        <v>460</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" t="s">
+        <v>461</v>
+      </c>
+      <c r="F50" t="s">
+        <v>31</v>
+      </c>
+      <c r="G50" t="s">
+        <v>31</v>
+      </c>
+      <c r="H50" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" t="s">
+        <v>461</v>
+      </c>
+      <c r="J50" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" t="s">
+        <v>24</v>
+      </c>
+      <c r="M50" t="s">
+        <v>462</v>
+      </c>
+      <c r="N50" t="s">
+        <v>24</v>
+      </c>
+      <c r="O50" t="s">
+        <v>461</v>
+      </c>
+      <c r="P50" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>463</v>
+      </c>
+      <c r="R50" t="s">
+        <v>24</v>
+      </c>
+      <c r="S50" t="s">
+        <v>461</v>
+      </c>
+      <c r="T50" t="s">
+        <v>24</v>
+      </c>
+      <c r="U50" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>450</v>
+      </c>
+      <c r="B51" t="s">
+        <v>465</v>
+      </c>
+      <c r="C51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" t="s">
+        <v>466</v>
+      </c>
+      <c r="F51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G51" t="s">
+        <v>31</v>
+      </c>
+      <c r="H51" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" t="s">
+        <v>463</v>
+      </c>
+      <c r="J51" t="s">
+        <v>24</v>
+      </c>
+      <c r="K51" t="s">
+        <v>463</v>
+      </c>
+      <c r="L51" t="s">
+        <v>24</v>
+      </c>
+      <c r="M51" t="s">
+        <v>463</v>
+      </c>
+      <c r="N51" t="s">
+        <v>24</v>
+      </c>
+      <c r="O51" t="s">
+        <v>463</v>
+      </c>
+      <c r="P51" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>463</v>
+      </c>
+      <c r="R51" t="s">
+        <v>24</v>
+      </c>
+      <c r="S51" t="s">
+        <v>463</v>
+      </c>
+      <c r="T51" t="s">
+        <v>24</v>
+      </c>
+      <c r="U51" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>450</v>
+      </c>
+      <c r="B52" t="s">
+        <v>467</v>
+      </c>
+      <c r="C52" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" t="s">
+        <v>468</v>
+      </c>
+      <c r="F52" t="s">
+        <v>31</v>
+      </c>
+      <c r="G52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H52" t="s">
+        <v>27</v>
+      </c>
+      <c r="I52" t="s">
+        <v>463</v>
+      </c>
+      <c r="J52" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" t="s">
+        <v>469</v>
+      </c>
+      <c r="L52" t="s">
+        <v>24</v>
+      </c>
+      <c r="M52" t="s">
+        <v>470</v>
+      </c>
+      <c r="N52" t="s">
+        <v>24</v>
+      </c>
+      <c r="O52" t="s">
+        <v>463</v>
+      </c>
+      <c r="P52" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>471</v>
+      </c>
+      <c r="R52" t="s">
+        <v>24</v>
+      </c>
+      <c r="S52" t="s">
+        <v>463</v>
+      </c>
+      <c r="T52" t="s">
+        <v>24</v>
+      </c>
+      <c r="U52" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>473</v>
+      </c>
+      <c r="B53" t="s">
+        <v>474</v>
+      </c>
+      <c r="C53" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" t="s">
+        <v>475</v>
+      </c>
+      <c r="F53" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" t="s">
+        <v>476</v>
+      </c>
+      <c r="H53" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" t="s">
+        <v>477</v>
+      </c>
+      <c r="J53" t="s">
+        <v>24</v>
+      </c>
+      <c r="K53" t="s">
+        <v>478</v>
+      </c>
+      <c r="L53" t="s">
+        <v>24</v>
+      </c>
+      <c r="M53" t="s">
+        <v>479</v>
+      </c>
+      <c r="N53" t="s">
+        <v>31</v>
+      </c>
+      <c r="O53" t="s">
+        <v>31</v>
+      </c>
+      <c r="P53" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>480</v>
+      </c>
+      <c r="R53" t="s">
+        <v>24</v>
+      </c>
+      <c r="S53" t="s">
+        <v>481</v>
+      </c>
+      <c r="T53" t="s">
+        <v>24</v>
+      </c>
+      <c r="U53" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>473</v>
+      </c>
+      <c r="B54" t="s">
+        <v>474</v>
+      </c>
+      <c r="C54" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" t="s">
+        <v>483</v>
+      </c>
+      <c r="F54" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54" t="s">
+        <v>31</v>
+      </c>
+      <c r="H54" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54" t="s">
+        <v>484</v>
+      </c>
+      <c r="J54" t="s">
+        <v>24</v>
+      </c>
+      <c r="K54" t="s">
+        <v>485</v>
+      </c>
+      <c r="L54" t="s">
+        <v>24</v>
+      </c>
+      <c r="M54" t="s">
+        <v>486</v>
+      </c>
+      <c r="N54" t="s">
+        <v>24</v>
+      </c>
+      <c r="O54" t="s">
+        <v>487</v>
+      </c>
+      <c r="P54" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>488</v>
+      </c>
+      <c r="R54" t="s">
+        <v>24</v>
+      </c>
+      <c r="S54" t="s">
+        <v>489</v>
+      </c>
+      <c r="T54" t="s">
+        <v>24</v>
+      </c>
+      <c r="U54" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>473</v>
+      </c>
+      <c r="B55" t="s">
+        <v>491</v>
+      </c>
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" t="s">
+        <v>492</v>
+      </c>
+      <c r="F55" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" t="s">
+        <v>492</v>
+      </c>
+      <c r="H55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I55" t="s">
+        <v>492</v>
+      </c>
+      <c r="J55" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" t="s">
+        <v>492</v>
+      </c>
+      <c r="L55" t="s">
+        <v>24</v>
+      </c>
+      <c r="M55" t="s">
+        <v>492</v>
+      </c>
+      <c r="N55" t="s">
+        <v>31</v>
+      </c>
+      <c r="O55" t="s">
+        <v>31</v>
+      </c>
+      <c r="P55" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>492</v>
+      </c>
+      <c r="R55" t="s">
+        <v>24</v>
+      </c>
+      <c r="S55" t="s">
+        <v>492</v>
+      </c>
+      <c r="T55" t="s">
+        <v>24</v>
+      </c>
+      <c r="U55" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>473</v>
+      </c>
+      <c r="B56" t="s">
+        <v>493</v>
+      </c>
+      <c r="C56" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" t="s">
+        <v>494</v>
+      </c>
+      <c r="F56" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" t="s">
+        <v>495</v>
+      </c>
+      <c r="H56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56" t="s">
+        <v>496</v>
+      </c>
+      <c r="J56" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" t="s">
+        <v>497</v>
+      </c>
+      <c r="L56" t="s">
+        <v>24</v>
+      </c>
+      <c r="M56" t="s">
+        <v>498</v>
+      </c>
+      <c r="N56" t="s">
+        <v>31</v>
+      </c>
+      <c r="O56" t="s">
+        <v>31</v>
+      </c>
+      <c r="P56" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>499</v>
+      </c>
+      <c r="R56" t="s">
+        <v>24</v>
+      </c>
+      <c r="S56" t="s">
+        <v>500</v>
+      </c>
+      <c r="T56" t="s">
+        <v>24</v>
+      </c>
+      <c r="U56" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>502</v>
+      </c>
+      <c r="B57" t="s">
+        <v>503</v>
+      </c>
+      <c r="C57" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" t="s">
+        <v>504</v>
+      </c>
+      <c r="F57" t="s">
+        <v>31</v>
+      </c>
+      <c r="G57" t="s">
+        <v>31</v>
+      </c>
+      <c r="H57" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57" t="s">
+        <v>505</v>
+      </c>
+      <c r="J57" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" t="s">
+        <v>506</v>
+      </c>
+      <c r="L57" t="s">
+        <v>24</v>
+      </c>
+      <c r="M57" t="s">
+        <v>507</v>
+      </c>
+      <c r="N57" t="s">
+        <v>24</v>
+      </c>
+      <c r="O57" t="s">
+        <v>508</v>
+      </c>
+      <c r="P57" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>509</v>
+      </c>
+      <c r="R57" t="s">
+        <v>24</v>
+      </c>
+      <c r="S57" t="s">
+        <v>510</v>
+      </c>
+      <c r="T57" t="s">
+        <v>24</v>
+      </c>
+      <c r="U57" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>502</v>
+      </c>
+      <c r="B58" t="s">
+        <v>512</v>
+      </c>
+      <c r="C58" t="s">
+        <v>23</v>
+      </c>
+      <c r="D58" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" t="s">
+        <v>513</v>
+      </c>
+      <c r="F58" t="s">
+        <v>31</v>
+      </c>
+      <c r="G58" t="s">
+        <v>31</v>
+      </c>
+      <c r="H58" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58" t="s">
+        <v>514</v>
+      </c>
+      <c r="J58" t="s">
+        <v>24</v>
+      </c>
+      <c r="K58" t="s">
+        <v>515</v>
+      </c>
+      <c r="L58" t="s">
+        <v>24</v>
+      </c>
+      <c r="M58" t="s">
+        <v>516</v>
+      </c>
+      <c r="N58" t="s">
+        <v>24</v>
+      </c>
+      <c r="O58" t="s">
+        <v>517</v>
+      </c>
+      <c r="P58" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>518</v>
+      </c>
+      <c r="R58" t="s">
+        <v>24</v>
+      </c>
+      <c r="S58" t="s">
+        <v>519</v>
+      </c>
+      <c r="T58" t="s">
+        <v>24</v>
+      </c>
+      <c r="U58" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>502</v>
+      </c>
+      <c r="B59" t="s">
+        <v>521</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" t="s">
+        <v>522</v>
+      </c>
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59" t="s">
+        <v>31</v>
+      </c>
+      <c r="H59" t="s">
+        <v>27</v>
+      </c>
+      <c r="I59" t="s">
+        <v>523</v>
+      </c>
+      <c r="J59" t="s">
+        <v>24</v>
+      </c>
+      <c r="K59" t="s">
+        <v>524</v>
+      </c>
+      <c r="L59" t="s">
+        <v>24</v>
+      </c>
+      <c r="M59" t="s">
+        <v>525</v>
+      </c>
+      <c r="N59" t="s">
+        <v>24</v>
+      </c>
+      <c r="O59" t="s">
+        <v>526</v>
+      </c>
+      <c r="P59" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>527</v>
+      </c>
+      <c r="R59" t="s">
+        <v>24</v>
+      </c>
+      <c r="S59" t="s">
+        <v>528</v>
+      </c>
+      <c r="T59" t="s">
+        <v>24</v>
+      </c>
+      <c r="U59" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>530</v>
+      </c>
+      <c r="B60" t="s">
+        <v>531</v>
+      </c>
+      <c r="C60" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" t="s">
+        <v>532</v>
+      </c>
+      <c r="F60" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" t="s">
+        <v>31</v>
+      </c>
+      <c r="H60" t="s">
+        <v>24</v>
+      </c>
+      <c r="I60" t="s">
+        <v>533</v>
+      </c>
+      <c r="J60" t="s">
+        <v>24</v>
+      </c>
+      <c r="K60" t="s">
+        <v>534</v>
+      </c>
+      <c r="L60" t="s">
+        <v>24</v>
+      </c>
+      <c r="M60" t="s">
+        <v>535</v>
+      </c>
+      <c r="N60" t="s">
+        <v>24</v>
+      </c>
+      <c r="O60" t="s">
+        <v>536</v>
+      </c>
+      <c r="P60" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>537</v>
+      </c>
+      <c r="R60" t="s">
+        <v>24</v>
+      </c>
+      <c r="S60" t="s">
+        <v>538</v>
+      </c>
+      <c r="T60" t="s">
+        <v>24</v>
+      </c>
+      <c r="U60" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>530</v>
+      </c>
+      <c r="B61" t="s">
         <v>35</v>
       </c>
-      <c r="F3" t="s">
+      <c r="C61" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
+      <c r="D61" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" t="s">
+        <v>540</v>
+      </c>
+      <c r="F61" t="s">
+        <v>31</v>
+      </c>
+      <c r="G61" t="s">
+        <v>31</v>
+      </c>
+      <c r="H61" t="s">
+        <v>24</v>
+      </c>
+      <c r="I61" t="s">
+        <v>541</v>
+      </c>
+      <c r="J61" t="s">
+        <v>24</v>
+      </c>
+      <c r="K61" t="s">
+        <v>542</v>
+      </c>
+      <c r="L61" t="s">
+        <v>24</v>
+      </c>
+      <c r="M61" t="s">
+        <v>543</v>
+      </c>
+      <c r="N61" t="s">
+        <v>24</v>
+      </c>
+      <c r="O61" t="s">
+        <v>544</v>
+      </c>
+      <c r="P61" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>545</v>
+      </c>
+      <c r="R61" t="s">
+        <v>24</v>
+      </c>
+      <c r="S61" t="s">
+        <v>546</v>
+      </c>
+      <c r="T61" t="s">
+        <v>24</v>
+      </c>
+      <c r="U61" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>530</v>
+      </c>
+      <c r="B62" t="s">
+        <v>548</v>
+      </c>
+      <c r="C62" t="s">
         <v>23</v>
       </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R3" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T3" t="s">
-        <v>22</v>
-      </c>
-      <c r="U3" t="s">
-        <v>38</v>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" t="s">
+        <v>549</v>
+      </c>
+      <c r="F62" t="s">
+        <v>31</v>
+      </c>
+      <c r="G62" t="s">
+        <v>31</v>
+      </c>
+      <c r="H62" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" t="s">
+        <v>550</v>
+      </c>
+      <c r="J62" t="s">
+        <v>24</v>
+      </c>
+      <c r="K62" t="s">
+        <v>551</v>
+      </c>
+      <c r="L62" t="s">
+        <v>24</v>
+      </c>
+      <c r="M62" t="s">
+        <v>552</v>
+      </c>
+      <c r="N62" t="s">
+        <v>24</v>
+      </c>
+      <c r="O62" t="s">
+        <v>553</v>
+      </c>
+      <c r="P62" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>554</v>
+      </c>
+      <c r="R62" t="s">
+        <v>24</v>
+      </c>
+      <c r="S62" t="s">
+        <v>555</v>
+      </c>
+      <c r="T62" t="s">
+        <v>24</v>
+      </c>
+      <c r="U62" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>557</v>
+      </c>
+      <c r="B63" t="s">
+        <v>558</v>
+      </c>
+      <c r="C63" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" t="s">
+        <v>559</v>
+      </c>
+      <c r="F63" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" t="s">
+        <v>31</v>
+      </c>
+      <c r="H63" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63" t="s">
+        <v>560</v>
+      </c>
+      <c r="J63" t="s">
+        <v>24</v>
+      </c>
+      <c r="K63" t="s">
+        <v>559</v>
+      </c>
+      <c r="L63" t="s">
+        <v>24</v>
+      </c>
+      <c r="M63" t="s">
+        <v>561</v>
+      </c>
+      <c r="N63" t="s">
+        <v>24</v>
+      </c>
+      <c r="O63" t="s">
+        <v>562</v>
+      </c>
+      <c r="P63" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>563</v>
+      </c>
+      <c r="R63" t="s">
+        <v>24</v>
+      </c>
+      <c r="S63" t="s">
+        <v>564</v>
+      </c>
+      <c r="T63" t="s">
+        <v>24</v>
+      </c>
+      <c r="U63" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>566</v>
+      </c>
+      <c r="B64" t="s">
+        <v>567</v>
+      </c>
+      <c r="C64" t="s">
+        <v>23</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" t="s">
+        <v>568</v>
+      </c>
+      <c r="F64" t="s">
+        <v>31</v>
+      </c>
+      <c r="G64" t="s">
+        <v>31</v>
+      </c>
+      <c r="H64" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64" t="s">
+        <v>569</v>
+      </c>
+      <c r="J64" t="s">
+        <v>27</v>
+      </c>
+      <c r="K64" t="s">
+        <v>570</v>
+      </c>
+      <c r="L64" t="s">
+        <v>24</v>
+      </c>
+      <c r="M64" t="s">
+        <v>571</v>
+      </c>
+      <c r="N64" t="s">
+        <v>24</v>
+      </c>
+      <c r="O64" t="s">
+        <v>572</v>
+      </c>
+      <c r="P64" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>573</v>
+      </c>
+      <c r="R64" t="s">
+        <v>24</v>
+      </c>
+      <c r="S64" t="s">
+        <v>574</v>
+      </c>
+      <c r="T64" t="s">
+        <v>24</v>
+      </c>
+      <c r="U64" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>576</v>
+      </c>
+      <c r="B65" t="s">
+        <v>577</v>
+      </c>
+      <c r="C65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" t="s">
+        <v>578</v>
+      </c>
+      <c r="F65" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" t="s">
+        <v>31</v>
+      </c>
+      <c r="H65" t="s">
+        <v>24</v>
+      </c>
+      <c r="I65" t="s">
+        <v>579</v>
+      </c>
+      <c r="J65" t="s">
+        <v>24</v>
+      </c>
+      <c r="K65" t="s">
+        <v>580</v>
+      </c>
+      <c r="L65" t="s">
+        <v>24</v>
+      </c>
+      <c r="M65" t="s">
+        <v>581</v>
+      </c>
+      <c r="N65" t="s">
+        <v>24</v>
+      </c>
+      <c r="O65" t="s">
+        <v>582</v>
+      </c>
+      <c r="P65" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>583</v>
+      </c>
+      <c r="R65" t="s">
+        <v>24</v>
+      </c>
+      <c r="S65" t="s">
+        <v>584</v>
+      </c>
+      <c r="T65" t="s">
+        <v>24</v>
+      </c>
+      <c r="U65" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>586</v>
+      </c>
+      <c r="B66" t="s">
+        <v>587</v>
+      </c>
+      <c r="C66" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" t="s">
+        <v>588</v>
+      </c>
+      <c r="F66" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66" t="s">
+        <v>31</v>
+      </c>
+      <c r="H66" t="s">
+        <v>24</v>
+      </c>
+      <c r="I66" t="s">
+        <v>589</v>
+      </c>
+      <c r="J66" t="s">
+        <v>24</v>
+      </c>
+      <c r="K66" t="s">
+        <v>590</v>
+      </c>
+      <c r="L66" t="s">
+        <v>24</v>
+      </c>
+      <c r="M66" t="s">
+        <v>591</v>
+      </c>
+      <c r="N66" t="s">
+        <v>24</v>
+      </c>
+      <c r="O66" t="s">
+        <v>592</v>
+      </c>
+      <c r="P66" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>593</v>
+      </c>
+      <c r="R66" t="s">
+        <v>24</v>
+      </c>
+      <c r="S66" t="s">
+        <v>594</v>
+      </c>
+      <c r="T66" t="s">
+        <v>24</v>
+      </c>
+      <c r="U66" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>586</v>
+      </c>
+      <c r="B67" t="s">
+        <v>596</v>
+      </c>
+      <c r="C67" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" t="s">
+        <v>597</v>
+      </c>
+      <c r="F67" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67" t="s">
+        <v>31</v>
+      </c>
+      <c r="H67" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67" t="s">
+        <v>598</v>
+      </c>
+      <c r="J67" t="s">
+        <v>24</v>
+      </c>
+      <c r="K67" t="s">
+        <v>599</v>
+      </c>
+      <c r="L67" t="s">
+        <v>24</v>
+      </c>
+      <c r="M67" t="s">
+        <v>600</v>
+      </c>
+      <c r="N67" t="s">
+        <v>24</v>
+      </c>
+      <c r="O67" t="s">
+        <v>601</v>
+      </c>
+      <c r="P67" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>602</v>
+      </c>
+      <c r="R67" t="s">
+        <v>24</v>
+      </c>
+      <c r="S67" t="s">
+        <v>603</v>
+      </c>
+      <c r="T67" t="s">
+        <v>24</v>
+      </c>
+      <c r="U67" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>586</v>
+      </c>
+      <c r="B68" t="s">
+        <v>605</v>
+      </c>
+      <c r="C68" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" t="s">
+        <v>606</v>
+      </c>
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" t="s">
+        <v>31</v>
+      </c>
+      <c r="H68" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68" t="s">
+        <v>607</v>
+      </c>
+      <c r="J68" t="s">
+        <v>24</v>
+      </c>
+      <c r="K68" t="s">
+        <v>608</v>
+      </c>
+      <c r="L68" t="s">
+        <v>24</v>
+      </c>
+      <c r="M68" t="s">
+        <v>609</v>
+      </c>
+      <c r="N68" t="s">
+        <v>24</v>
+      </c>
+      <c r="O68" t="s">
+        <v>610</v>
+      </c>
+      <c r="P68" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>611</v>
+      </c>
+      <c r="R68" t="s">
+        <v>24</v>
+      </c>
+      <c r="S68" t="s">
+        <v>612</v>
+      </c>
+      <c r="T68" t="s">
+        <v>27</v>
+      </c>
+      <c r="U68" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>586</v>
+      </c>
+      <c r="B69" t="s">
+        <v>376</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" t="s">
+        <v>614</v>
+      </c>
+      <c r="F69" t="s">
+        <v>31</v>
+      </c>
+      <c r="G69" t="s">
+        <v>31</v>
+      </c>
+      <c r="H69" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69" t="s">
+        <v>615</v>
+      </c>
+      <c r="J69" t="s">
+        <v>24</v>
+      </c>
+      <c r="K69" t="s">
+        <v>616</v>
+      </c>
+      <c r="L69" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" t="s">
+        <v>617</v>
+      </c>
+      <c r="N69" t="s">
+        <v>24</v>
+      </c>
+      <c r="O69" t="s">
+        <v>618</v>
+      </c>
+      <c r="P69" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>619</v>
+      </c>
+      <c r="R69" t="s">
+        <v>24</v>
+      </c>
+      <c r="S69" t="s">
+        <v>620</v>
+      </c>
+      <c r="T69" t="s">
+        <v>24</v>
+      </c>
+      <c r="U69" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>622</v>
+      </c>
+      <c r="B70" t="s">
+        <v>623</v>
+      </c>
+      <c r="C70" t="s">
+        <v>23</v>
+      </c>
+      <c r="D70" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" t="s">
+        <v>624</v>
+      </c>
+      <c r="F70" t="s">
+        <v>31</v>
+      </c>
+      <c r="G70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H70" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" t="s">
+        <v>625</v>
+      </c>
+      <c r="J70" t="s">
+        <v>27</v>
+      </c>
+      <c r="K70" t="s">
+        <v>626</v>
+      </c>
+      <c r="L70" t="s">
+        <v>24</v>
+      </c>
+      <c r="M70" t="s">
+        <v>627</v>
+      </c>
+      <c r="N70" t="s">
+        <v>24</v>
+      </c>
+      <c r="O70" t="s">
+        <v>628</v>
+      </c>
+      <c r="P70" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>629</v>
+      </c>
+      <c r="R70" t="s">
+        <v>24</v>
+      </c>
+      <c r="S70" t="s">
+        <v>630</v>
+      </c>
+      <c r="T70" t="s">
+        <v>24</v>
+      </c>
+      <c r="U70" t="s">
+        <v>631</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>